--- a/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
@@ -74423,28 +74423,28 @@
         <v>-1</v>
       </c>
       <c r="BG154" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH154" t="n">
         <v>1</v>
       </c>
       <c r="BI154" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ154" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK154" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BL154" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BM154" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN154" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO154" t="n">
         <v>0</v>
@@ -74519,10 +74519,10 @@
         <v>0</v>
       </c>
       <c r="CM154" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN154" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO154" t="n">
         <v>0</v>

--- a/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
@@ -79619,13 +79619,13 @@
         <v>3</v>
       </c>
       <c r="S165" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T165" t="n">
         <v>17</v>
       </c>
       <c r="U165" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V165" t="n">
         <v>20</v>
@@ -79637,10 +79637,10 @@
         <v>11</v>
       </c>
       <c r="Y165" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z165" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
@@ -79800,13 +79800,13 @@
         <v>142</v>
       </c>
       <c r="BZ165" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="CA165" t="n">
         <v>2.1</v>
       </c>
       <c r="CB165" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="CC165" t="n">
         <v>0</v>
@@ -79875,7 +79875,7 @@
         <v>14</v>
       </c>
       <c r="CY165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ165" t="n">
         <v>29</v>
@@ -79964,68 +79964,68 @@
       </c>
       <c r="EA165" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB165" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EC165" t="inlineStr">
         <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="ED165" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EE165" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EF165" t="inlineStr"/>
-      <c r="EG165" t="inlineStr"/>
-      <c r="EH165" t="inlineStr"/>
-      <c r="EI165" t="inlineStr"/>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="ED165" t="inlineStr"/>
+      <c r="EE165" t="inlineStr"/>
+      <c r="EF165" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EG165" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EH165" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EI165" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
       <c r="EJ165" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EK165" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EL165" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EM165" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EN165" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EO165" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EP165" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EO165" t="inlineStr"/>
+      <c r="EP165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP167" headerRowCount="1">
-  <autoFilter ref="A1:EP167"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP169" headerRowCount="1">
+  <autoFilter ref="A1:EP169"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP167"/>
+  <dimension ref="A1:EP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -7133,7 +7133,7 @@
         <v>1.88</v>
       </c>
       <c r="DE13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -9050,7 +9050,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE17" t="n">
         <v>0.86</v>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10017,7 +10017,7 @@
         <v>2.14</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -10486,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE20" t="n">
         <v>1.5</v>
@@ -12935,7 +12935,7 @@
         <v>1.8</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -14837,7 +14837,7 @@
         <v>1.29</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DF29" t="n">
         <v>0</v>
@@ -14867,7 +14867,7 @@
         <v>1.12</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -19657,7 +19657,7 @@
         <v>1.88</v>
       </c>
       <c r="DE39" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -20134,7 +20134,7 @@
         <v>100</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE40" t="n">
         <v>0.43</v>
@@ -21574,7 +21574,7 @@
         <v>0</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE43" t="n">
         <v>1.63</v>
@@ -26777,7 +26777,7 @@
         <v>1.67</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DF54" t="n">
         <v>3</v>
@@ -26807,7 +26807,7 @@
         <v>2.74</v>
       </c>
       <c r="DO54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -28666,7 +28666,7 @@
         <v>50</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE58" t="n">
         <v>1.38</v>
@@ -30562,7 +30562,7 @@
         <v>75</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE62" t="n">
         <v>0.88</v>
@@ -32949,7 +32949,7 @@
         <v>1.5</v>
       </c>
       <c r="DE67" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -32979,7 +32979,7 @@
         <v>2.52</v>
       </c>
       <c r="DO67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -37793,7 +37793,7 @@
         <v>1.88</v>
       </c>
       <c r="DE77" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF77" t="n">
         <v>2.33</v>
@@ -38722,7 +38722,7 @@
         <v>50</v>
       </c>
       <c r="DD79" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE79" t="n">
         <v>0.29</v>
@@ -40165,7 +40165,7 @@
         <v>1.88</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DF82" t="n">
         <v>1.75</v>
@@ -43534,7 +43534,7 @@
         <v>54</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE89" t="n">
         <v>1.13</v>
@@ -49273,7 +49273,7 @@
         <v>1.29</v>
       </c>
       <c r="DE101" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF101" t="n">
         <v>1.75</v>
@@ -49303,7 +49303,7 @@
         <v>2.63</v>
       </c>
       <c r="DO101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP101" t="b">
         <v>0</v>
@@ -49750,7 +49750,7 @@
         <v>78</v>
       </c>
       <c r="DD102" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE102" t="n">
         <v>1</v>
@@ -53541,7 +53541,7 @@
         <v>1.75</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DF110" t="n">
         <v>2.6</v>
@@ -54482,7 +54482,7 @@
         <v>43</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE112" t="n">
         <v>0.75</v>
@@ -54515,7 +54515,7 @@
         <v>1.89</v>
       </c>
       <c r="DO112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54651,170 +54651,170 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
         <v>45955.59375</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
+        <v>7</v>
+      </c>
+      <c r="K113" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" t="n">
         <v>9</v>
       </c>
-      <c r="K113" t="n">
-        <v>4</v>
-      </c>
-      <c r="L113" t="n">
+      <c r="M113" t="n">
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>5</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>3</v>
+      </c>
+      <c r="R113" t="n">
+        <v>3</v>
+      </c>
+      <c r="S113" t="n">
+        <v>9</v>
+      </c>
+      <c r="T113" t="n">
+        <v>6</v>
+      </c>
+      <c r="U113" t="n">
+        <v>12</v>
+      </c>
+      <c r="V113" t="n">
+        <v>9</v>
+      </c>
+      <c r="W113" t="n">
         <v>13</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>4</v>
-      </c>
-      <c r="R113" t="n">
-        <v>9</v>
-      </c>
-      <c r="S113" t="n">
-        <v>17</v>
-      </c>
-      <c r="T113" t="n">
-        <v>4</v>
-      </c>
-      <c r="U113" t="n">
-        <v>21</v>
-      </c>
-      <c r="V113" t="n">
-        <v>13</v>
-      </c>
-      <c r="W113" t="n">
-        <v>8</v>
       </c>
       <c r="X113" t="n">
         <v>10</v>
       </c>
       <c r="Y113" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Z113" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Estadio Carlos Belmonte</t>
+          <t>Estadio Municipal de Ipurúa</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Avenida de España, Albacete</t>
+          <t>Calle de Ipurúa, Eibar</t>
         </is>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE113" t="n">
         <v>2.15</v>
       </c>
       <c r="AF113" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AG113" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI113" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AJ113" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="AK113" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM113" t="n">
         <v>1.65</v>
       </c>
-      <c r="AL113" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AN113" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AO113" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AR113" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AS113" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AT113" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV113" t="n">
         <v>0</v>
       </c>
       <c r="AW113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB113" t="n">
-        <v>294</v>
+        <v>-1</v>
       </c>
       <c r="BC113" t="n">
         <v>0</v>
       </c>
       <c r="BD113" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BE113" t="n">
         <v>0</v>
@@ -54826,67 +54826,67 @@
         <v>2</v>
       </c>
       <c r="BH113" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI113" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS113" t="n">
         <v>4</v>
       </c>
-      <c r="BJ113" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK113" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL113" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM113" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN113" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS113" t="n">
-        <v>0</v>
-      </c>
       <c r="BT113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU113" t="n">
         <v>1</v>
       </c>
       <c r="BV113" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="BW113" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BX113" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="BY113" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="BZ113" t="n">
-        <v>2.06</v>
+        <v>1.49</v>
       </c>
       <c r="CA113" t="n">
-        <v>1.66</v>
+        <v>0.98</v>
       </c>
       <c r="CB113" t="n">
-        <v>3.72</v>
+        <v>2.47</v>
       </c>
       <c r="CC113" t="n">
         <v>0</v>
@@ -54916,28 +54916,28 @@
         <v>0</v>
       </c>
       <c r="CL113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN113" t="n">
         <v>1</v>
       </c>
       <c r="CO113" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP113" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ113" t="n">
         <v>1</v>
       </c>
       <c r="CR113" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="CS113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT113" t="n">
         <v>1</v>
@@ -54946,76 +54946,76 @@
         <v>10</v>
       </c>
       <c r="CV113" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CW113" t="n">
         <v>1</v>
       </c>
       <c r="CX113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CY113" t="n">
         <v>11</v>
       </c>
       <c r="CZ113" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="DA113" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="DB113" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DC113" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="DF113" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="DG113" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="DH113" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="DI113" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="DJ113" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="DK113" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="DL113" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="DM113" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="DN113" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DO113" t="n">
         <v>15</v>
       </c>
       <c r="DP113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT113" t="b">
         <v>0</v>
@@ -55024,88 +55024,96 @@
         <v>0</v>
       </c>
       <c r="DV113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW113" t="n">
-        <v>23.67</v>
+        <v>12.38</v>
       </c>
       <c r="DX113" t="n">
-        <v>8.06</v>
+        <v>1.29</v>
       </c>
       <c r="DY113" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="DZ113" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA113" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EB113" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EC113" t="inlineStr">
         <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="ED113" t="inlineStr"/>
-      <c r="EE113" t="inlineStr"/>
-      <c r="EF113" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="EG113" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="ED113" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EE113" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF113" t="inlineStr"/>
+      <c r="EG113" t="inlineStr"/>
       <c r="EH113" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EI113" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EJ113" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EK113" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="EL113" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EM113" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EN113" t="inlineStr">
         <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EO113" t="inlineStr"/>
-      <c r="EP113" t="inlineStr"/>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EO113" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EP113" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -55123,170 +55131,170 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
         <v>45955.59375</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L114" t="n">
+        <v>13</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>4</v>
+      </c>
+      <c r="R114" t="n">
         <v>9</v>
       </c>
-      <c r="M114" t="n">
-        <v>2</v>
-      </c>
-      <c r="N114" t="n">
-        <v>5</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>3</v>
-      </c>
-      <c r="R114" t="n">
-        <v>3</v>
-      </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U114" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W114" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="X114" t="n">
         <v>10</v>
       </c>
       <c r="Y114" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Z114" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Ipurúa</t>
+          <t>Estadio Carlos Belmonte</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Calle de Ipurúa, Eibar</t>
+          <t>Avenida de España, Albacete</t>
         </is>
       </c>
       <c r="AC114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE114" t="n">
         <v>2.15</v>
       </c>
       <c r="AF114" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AG114" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AH114" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT114" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI114" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ114" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK114" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL114" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AM114" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AN114" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AO114" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AP114" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AQ114" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR114" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS114" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT114" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AU114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV114" t="n">
         <v>0</v>
       </c>
       <c r="AW114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB114" t="n">
-        <v>-1</v>
+        <v>294</v>
       </c>
       <c r="BC114" t="n">
         <v>0</v>
       </c>
       <c r="BD114" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BE114" t="n">
         <v>0</v>
@@ -55298,67 +55306,67 @@
         <v>2</v>
       </c>
       <c r="BH114" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK114" t="n">
         <v>5</v>
       </c>
-      <c r="BJ114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK114" t="n">
-        <v>2</v>
-      </c>
       <c r="BL114" t="n">
         <v>1</v>
       </c>
       <c r="BM114" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN114" t="n">
         <v>6</v>
       </c>
-      <c r="BN114" t="n">
-        <v>3</v>
-      </c>
       <c r="BO114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS114" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU114" t="n">
         <v>1</v>
       </c>
       <c r="BV114" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="BW114" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BX114" t="n">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="BY114" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="BZ114" t="n">
-        <v>1.49</v>
+        <v>2.06</v>
       </c>
       <c r="CA114" t="n">
-        <v>0.98</v>
+        <v>1.66</v>
       </c>
       <c r="CB114" t="n">
-        <v>2.47</v>
+        <v>3.72</v>
       </c>
       <c r="CC114" t="n">
         <v>0</v>
@@ -55388,28 +55396,28 @@
         <v>0</v>
       </c>
       <c r="CL114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN114" t="n">
         <v>1</v>
       </c>
       <c r="CO114" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP114" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ114" t="n">
         <v>1</v>
       </c>
       <c r="CR114" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="CS114" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CT114" t="n">
         <v>1</v>
@@ -55418,76 +55426,76 @@
         <v>10</v>
       </c>
       <c r="CV114" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CW114" t="n">
         <v>1</v>
       </c>
       <c r="CX114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CY114" t="n">
         <v>11</v>
       </c>
       <c r="CZ114" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="DA114" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="DB114" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DC114" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="DF114" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="DG114" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="DH114" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="DI114" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="DJ114" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="DK114" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="DL114" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="DM114" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="DN114" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="DO114" t="n">
         <v>15</v>
       </c>
       <c r="DP114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT114" t="b">
         <v>0</v>
@@ -55496,96 +55504,88 @@
         <v>0</v>
       </c>
       <c r="DV114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW114" t="n">
-        <v>12.38</v>
+        <v>23.67</v>
       </c>
       <c r="DX114" t="n">
-        <v>1.29</v>
+        <v>8.06</v>
       </c>
       <c r="DY114" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="DZ114" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA114" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EB114" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EC114" t="inlineStr">
         <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="ED114" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EE114" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EF114" t="inlineStr"/>
-      <c r="EG114" t="inlineStr"/>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="ED114" t="inlineStr"/>
+      <c r="EE114" t="inlineStr"/>
+      <c r="EF114" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EG114" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
       <c r="EH114" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EI114" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="EJ114" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EK114" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EL114" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EM114" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EN114" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EO114" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EP114" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EO114" t="inlineStr"/>
+      <c r="EP114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -55603,40 +55603,40 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45955.6875</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K115" t="n">
+        <v>3</v>
+      </c>
+      <c r="L115" t="n">
+        <v>9</v>
+      </c>
+      <c r="M115" t="n">
         <v>4</v>
       </c>
-      <c r="L115" t="n">
-        <v>12</v>
-      </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -55645,101 +55645,101 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
         <v>1</v>
       </c>
       <c r="S115" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T115" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="W115" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X115" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y115" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="Z115" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Estadio Nuevo Los Cármenes</t>
+          <t>Estadio Municipal de El Plantío</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Calle Pintor Manuel Maldonado, Granada</t>
+          <t>Calle del Dos de Mayo, Burgos</t>
         </is>
       </c>
       <c r="AC115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE115" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK115" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF115" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH115" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK115" t="n">
-        <v>2</v>
-      </c>
       <c r="AL115" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AU115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV115" t="n">
         <v>0</v>
@@ -55748,25 +55748,25 @@
         <v>0</v>
       </c>
       <c r="AX115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY115" t="n">
         <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA115" t="n">
         <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>-1</v>
+        <v>4546</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55781,37 +55781,37 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BL115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM115" t="n">
         <v>5</v>
       </c>
       <c r="BN115" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BO115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BT115" t="n">
         <v>3</v>
@@ -55820,34 +55820,34 @@
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="BW115" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BX115" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="BY115" t="n">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="BZ115" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="CA115" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="CC115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD115" t="n">
         <v>0</v>
       </c>
       <c r="CE115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF115" t="n">
         <v>0</v>
@@ -55871,10 +55871,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55889,76 +55889,76 @@
         <v>24</v>
       </c>
       <c r="CS115" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CV115" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CZ115" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>68</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>58</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ115" t="n">
         <v>43</v>
       </c>
-      <c r="DA115" t="n">
-        <v>65</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>23</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>68</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DH115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI115" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DJ115" t="n">
-        <v>58</v>
-      </c>
       <c r="DK115" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="DM115" t="n">
-        <v>0.98</v>
+        <v>1.19</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="DO115" t="n">
         <v>15</v>
       </c>
       <c r="DP115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ115" t="b">
         <v>0</v>
@@ -55979,91 +55979,91 @@
         <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>25.8</v>
+        <v>12.02</v>
       </c>
       <c r="DX115" t="n">
-        <v>2.62</v>
+        <v>4.53</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="ED115" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EE115" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EF115" t="inlineStr"/>
       <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EN115" t="inlineStr">
+        <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="EI115" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="EJ115" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="EL115" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EM115" t="inlineStr">
+      <c r="EO115" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="EN115" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EO115" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -56083,40 +56083,40 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45955.6875</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L116" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -56125,101 +56125,101 @@
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
         <v>1</v>
       </c>
       <c r="S116" t="n">
+        <v>17</v>
+      </c>
+      <c r="T116" t="n">
+        <v>10</v>
+      </c>
+      <c r="U116" t="n">
+        <v>18</v>
+      </c>
+      <c r="V116" t="n">
         <v>11</v>
       </c>
-      <c r="T116" t="n">
-        <v>4</v>
-      </c>
-      <c r="U116" t="n">
-        <v>14</v>
-      </c>
-      <c r="V116" t="n">
-        <v>5</v>
-      </c>
       <c r="W116" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X116" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y116" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Z116" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Estadio Municipal de El Plantío</t>
+          <t>Estadio Nuevo Los Cármenes</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>Calle del Dos de Mayo, Burgos</t>
+          <t>Calle Pintor Manuel Maldonado, Granada</t>
         </is>
       </c>
       <c r="AC116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE116" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM116" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF116" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG116" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AH116" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI116" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AK116" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL116" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM116" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AN116" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AO116" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AP116" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ116" t="n">
         <v>1.45</v>
       </c>
-      <c r="AQ116" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR116" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AU116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV116" t="n">
         <v>0</v>
@@ -56228,25 +56228,25 @@
         <v>0</v>
       </c>
       <c r="AX116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY116" t="n">
         <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA116" t="n">
         <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>4546</v>
+        <v>-1</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56261,37 +56261,37 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BJ116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BL116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM116" t="n">
         <v>5</v>
       </c>
       <c r="BN116" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT116" t="n">
         <v>3</v>
@@ -56300,34 +56300,34 @@
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="BW116" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BX116" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="BY116" t="n">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="BZ116" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CA116" t="n">
-        <v>0.59</v>
+        <v>0.96</v>
       </c>
       <c r="CB116" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="CC116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD116" t="n">
         <v>0</v>
       </c>
       <c r="CE116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF116" t="n">
         <v>0</v>
@@ -56351,10 +56351,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56369,76 +56369,76 @@
         <v>24</v>
       </c>
       <c r="CS116" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CV116" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY116" t="n">
         <v>13</v>
       </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY116" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ116" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ116" t="n">
         <v>58</v>
       </c>
-      <c r="DA116" t="n">
-        <v>68</v>
-      </c>
-      <c r="DB116" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC116" t="n">
-        <v>58</v>
-      </c>
-      <c r="DD116" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF116" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH116" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ116" t="n">
-        <v>43</v>
-      </c>
       <c r="DK116" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.19</v>
+        <v>0.98</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DO116" t="n">
         <v>15</v>
       </c>
       <c r="DP116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ116" t="b">
         <v>0</v>
@@ -56459,91 +56459,91 @@
         <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>12.02</v>
+        <v>25.8</v>
       </c>
       <c r="DX116" t="n">
-        <v>4.53</v>
+        <v>2.62</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="ED116" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EE116" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EF116" t="inlineStr"/>
       <c r="EG116" t="inlineStr"/>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EK116" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="EL116" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EM116" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN116" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -59770,7 +59770,7 @@
         <v>62</v>
       </c>
       <c r="DD123" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE123" t="n">
         <v>1</v>
@@ -59939,40 +59939,40 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
         <v>45962.72916666666</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I124" t="n">
         <v>3</v>
       </c>
       <c r="J124" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K124" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L124" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M124" t="n">
         <v>3</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -59981,128 +59981,128 @@
         <v>0</v>
       </c>
       <c r="Q124" t="n">
+        <v>3</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="n">
+        <v>4</v>
+      </c>
+      <c r="U124" t="n">
+        <v>13</v>
+      </c>
+      <c r="V124" t="n">
         <v>6</v>
       </c>
-      <c r="R124" t="n">
-        <v>4</v>
-      </c>
-      <c r="S124" t="n">
-        <v>8</v>
-      </c>
-      <c r="T124" t="n">
+      <c r="W124" t="n">
         <v>17</v>
       </c>
-      <c r="U124" t="n">
-        <v>14</v>
-      </c>
-      <c r="V124" t="n">
-        <v>21</v>
-      </c>
-      <c r="W124" t="n">
-        <v>13</v>
-      </c>
       <c r="X124" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Y124" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="Z124" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Calle Arquitectura, Leganés</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>4546</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
         <v>60</v>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Estadio Carlos Belmonte</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>Avenida de España, Albacete</t>
-        </is>
-      </c>
-      <c r="AC124" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF124" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG124" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK124" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL124" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM124" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN124" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO124" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP124" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ124" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR124" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AS124" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT124" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AU124" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX124" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ124" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB124" t="n">
-        <v>316</v>
-      </c>
-      <c r="BC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD124" t="n">
-        <v>43</v>
       </c>
       <c r="BE124" t="n">
         <v>0</v>
@@ -60117,37 +60117,37 @@
         <v>1</v>
       </c>
       <c r="BI124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN124" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BO124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT124" t="n">
         <v>3</v>
@@ -60156,25 +60156,25 @@
         <v>1</v>
       </c>
       <c r="BV124" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BW124" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="BX124" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="BY124" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="BZ124" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="CA124" t="n">
-        <v>1.99</v>
+        <v>0.71</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.59</v>
+        <v>2.14</v>
       </c>
       <c r="CC124" t="n">
         <v>0</v>
@@ -60201,16 +60201,16 @@
         <v>1</v>
       </c>
       <c r="CK124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO124" t="n">
         <v>0</v>
@@ -60222,73 +60222,73 @@
         <v>1</v>
       </c>
       <c r="CR124" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CS124" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CT124" t="n">
         <v>1</v>
       </c>
       <c r="CU124" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
         <v>6</v>
       </c>
-      <c r="CV124" t="n">
+      <c r="CY124" t="n">
         <v>13</v>
       </c>
-      <c r="CW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX124" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY124" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ124" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="DA124" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="DB124" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="DC124" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.43</v>
+        <v>0.71</v>
       </c>
       <c r="DE124" t="n">
-        <v>0.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF124" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DG124" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="DH124" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM124" t="n">
         <v>1.18</v>
       </c>
-      <c r="DI124" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ124" t="n">
-        <v>45</v>
-      </c>
-      <c r="DK124" t="n">
-        <v>35</v>
-      </c>
-      <c r="DL124" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="DM124" t="n">
-        <v>0.72</v>
-      </c>
       <c r="DN124" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="DO124" t="n">
         <v>15</v>
@@ -60315,91 +60315,91 @@
         <v>1</v>
       </c>
       <c r="DW124" t="n">
-        <v>19.22</v>
+        <v>14.8</v>
       </c>
       <c r="DX124" t="n">
-        <v>7.18</v>
+        <v>6.8</v>
       </c>
       <c r="DY124" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ124" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EC124" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="ED124" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE124" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EF124" t="inlineStr"/>
       <c r="EG124" t="inlineStr"/>
       <c r="EH124" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EI124" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EJ124" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EK124" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="EL124" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EM124" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EN124" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EO124" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EP124" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -60419,170 +60419,170 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
         <v>45962.72916666666</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I125" t="n">
         <v>3</v>
       </c>
       <c r="J125" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K125" t="n">
+        <v>7</v>
+      </c>
+      <c r="L125" t="n">
+        <v>14</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>6</v>
+      </c>
+      <c r="R125" t="n">
         <v>4</v>
       </c>
-      <c r="L125" t="n">
+      <c r="S125" t="n">
+        <v>8</v>
+      </c>
+      <c r="T125" t="n">
+        <v>17</v>
+      </c>
+      <c r="U125" t="n">
+        <v>14</v>
+      </c>
+      <c r="V125" t="n">
+        <v>21</v>
+      </c>
+      <c r="W125" t="n">
         <v>13</v>
       </c>
-      <c r="M125" t="n">
-        <v>3</v>
-      </c>
-      <c r="N125" t="n">
-        <v>3</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>3</v>
-      </c>
-      <c r="R125" t="n">
-        <v>2</v>
-      </c>
-      <c r="S125" t="n">
-        <v>10</v>
-      </c>
-      <c r="T125" t="n">
-        <v>4</v>
-      </c>
-      <c r="U125" t="n">
-        <v>13</v>
-      </c>
-      <c r="V125" t="n">
+      <c r="X125" t="n">
         <v>6</v>
       </c>
-      <c r="W125" t="n">
-        <v>17</v>
-      </c>
-      <c r="X125" t="n">
-        <v>17</v>
-      </c>
       <c r="Y125" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="Z125" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque</t>
+          <t>Estadio Carlos Belmonte</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>Calle Arquitectura, Leganés</t>
+          <t>Avenida de España, Albacete</t>
         </is>
       </c>
       <c r="AC125" t="n">
         <v>3</v>
       </c>
       <c r="AD125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AF125" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AG125" t="n">
-        <v>3.92</v>
+        <v>3.79</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AI125" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS125" t="n">
         <v>2.45</v>
       </c>
-      <c r="AJ125" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AT125" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AU125" t="n">
         <v>3</v>
       </c>
       <c r="AV125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY125" t="n">
         <v>0</v>
       </c>
       <c r="AZ125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB125" t="n">
-        <v>4546</v>
+        <v>316</v>
       </c>
       <c r="BC125" t="n">
         <v>0</v>
       </c>
       <c r="BD125" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="BE125" t="n">
         <v>0</v>
@@ -60597,178 +60597,178 @@
         <v>1</v>
       </c>
       <c r="BI125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM125" t="n">
         <v>7</v>
       </c>
-      <c r="BJ125" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK125" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL125" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM125" t="n">
-        <v>8</v>
-      </c>
       <c r="BN125" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY125" t="n">
         <v>5</v>
       </c>
-      <c r="BO125" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP125" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ125" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR125" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS125" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT125" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU125" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV125" t="n">
+      <c r="CZ125" t="n">
         <v>55</v>
       </c>
-      <c r="BW125" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX125" t="n">
-        <v>88</v>
-      </c>
-      <c r="BY125" t="n">
-        <v>68</v>
-      </c>
-      <c r="BZ125" t="n">
+      <c r="DA125" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>58</v>
+      </c>
+      <c r="DD125" t="n">
         <v>1.43</v>
       </c>
-      <c r="CA125" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="CB125" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR125" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS125" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU125" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV125" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX125" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY125" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ125" t="n">
-        <v>50</v>
-      </c>
-      <c r="DA125" t="n">
-        <v>70</v>
-      </c>
-      <c r="DB125" t="n">
-        <v>30</v>
-      </c>
-      <c r="DC125" t="n">
-        <v>80</v>
-      </c>
-      <c r="DD125" t="n">
-        <v>0.71</v>
-      </c>
       <c r="DE125" t="n">
-        <v>1.86</v>
+        <v>0.43</v>
       </c>
       <c r="DF125" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DG125" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI125" t="n">
         <v>1.4</v>
       </c>
-      <c r="DH125" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DI125" t="n">
-        <v>1.64</v>
-      </c>
       <c r="DJ125" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DK125" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="DL125" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="DM125" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
       <c r="DN125" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="DO125" t="n">
         <v>15</v>
@@ -60795,91 +60795,91 @@
         <v>1</v>
       </c>
       <c r="DW125" t="n">
-        <v>14.8</v>
+        <v>19.22</v>
       </c>
       <c r="DX125" t="n">
-        <v>6.8</v>
+        <v>7.18</v>
       </c>
       <c r="DY125" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ125" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="EA125" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EB125" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EC125" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="ED125" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EE125" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EF125" t="inlineStr"/>
       <c r="EG125" t="inlineStr"/>
       <c r="EH125" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EI125" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EJ125" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EK125" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="EL125" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EM125" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EN125" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EO125" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EP125" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.34</t>
         </is>
       </c>
     </row>
@@ -61843,40 +61843,40 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
         <v>45963.63541666666</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L128" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M128" t="n">
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -61885,96 +61885,104 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R128" t="n">
         <v>2</v>
       </c>
       <c r="S128" t="n">
+        <v>8</v>
+      </c>
+      <c r="T128" t="n">
+        <v>10</v>
+      </c>
+      <c r="U128" t="n">
+        <v>12</v>
+      </c>
+      <c r="V128" t="n">
+        <v>12</v>
+      </c>
+      <c r="W128" t="n">
+        <v>18</v>
+      </c>
+      <c r="X128" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Arcángel</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Avenida del Arcángel, Córdoba</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD128" t="n">
         <v>4</v>
       </c>
-      <c r="T128" t="n">
-        <v>6</v>
-      </c>
-      <c r="U128" t="n">
-        <v>5</v>
-      </c>
-      <c r="V128" t="n">
-        <v>8</v>
-      </c>
-      <c r="W128" t="n">
-        <v>21</v>
-      </c>
-      <c r="X128" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>68</v>
-      </c>
-      <c r="AA128" t="inlineStr"/>
-      <c r="AB128" t="inlineStr"/>
-      <c r="AC128" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>2</v>
-      </c>
       <c r="AE128" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AF128" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AG128" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AI128" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AJ128" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AK128" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL128" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AM128" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AN128" t="n">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="AO128" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AR128" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="AS128" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AT128" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AU128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW128" t="n">
         <v>0</v>
@@ -61989,16 +61997,16 @@
         <v>0</v>
       </c>
       <c r="BA128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB128" t="n">
-        <v>-1</v>
+        <v>294</v>
       </c>
       <c r="BC128" t="n">
         <v>0</v>
       </c>
       <c r="BD128" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BE128" t="n">
         <v>0</v>
@@ -62013,64 +62021,64 @@
         <v>1</v>
       </c>
       <c r="BI128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ128" t="n">
         <v>3</v>
       </c>
       <c r="BK128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM128" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN128" t="n">
         <v>4</v>
       </c>
-      <c r="BN128" t="n">
-        <v>1</v>
-      </c>
       <c r="BO128" t="n">
         <v>1</v>
       </c>
       <c r="BP128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ128" t="n">
         <v>1</v>
       </c>
       <c r="BR128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU128" t="n">
         <v>1</v>
       </c>
       <c r="BV128" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="BW128" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="BX128" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="BY128" t="n">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="BZ128" t="n">
-        <v>0.63</v>
+        <v>1.51</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="CB128" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>
@@ -62097,16 +62105,16 @@
         <v>1</v>
       </c>
       <c r="CK128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL128" t="n">
         <v>0</v>
       </c>
       <c r="CM128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO128" t="n">
         <v>0</v>
@@ -62118,82 +62126,82 @@
         <v>1</v>
       </c>
       <c r="CR128" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV128" t="n">
         <v>18</v>
       </c>
-      <c r="CS128" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT128" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU128" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV128" t="n">
-        <v>21</v>
-      </c>
       <c r="CW128" t="n">
         <v>1</v>
       </c>
       <c r="CX128" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY128" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CZ128" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="DA128" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="DB128" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="DC128" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF128" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="DG128" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="DH128" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DI128" t="n">
         <v>1.64</v>
       </c>
-      <c r="DI128" t="n">
-        <v>1.73</v>
-      </c>
       <c r="DJ128" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="DK128" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="DL128" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="DM128" t="n">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="DN128" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DO128" t="n">
         <v>15</v>
       </c>
       <c r="DP128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR128" t="b">
         <v>0</v>
@@ -62211,69 +62219,101 @@
         <v>0</v>
       </c>
       <c r="DW128" t="n">
-        <v>18.47</v>
+        <v>26.22</v>
       </c>
       <c r="DX128" t="n">
-        <v>4.08</v>
+        <v>2.9</v>
       </c>
       <c r="DY128" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="DZ128" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA128" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EB128" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EC128" t="inlineStr">
         <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="ED128" t="inlineStr"/>
-      <c r="EE128" t="inlineStr"/>
-      <c r="EF128" t="inlineStr"/>
-      <c r="EG128" t="inlineStr"/>
-      <c r="EH128" t="inlineStr"/>
-      <c r="EI128" t="inlineStr"/>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EE128" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
       <c r="EJ128" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EK128" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="EL128" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EM128" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EN128" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EO128" t="inlineStr"/>
-      <c r="EP128" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EO128" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EP128" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -62291,146 +62331,138 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F129" s="2" t="n">
         <v>45963.63541666666</v>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
+        <v>2</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3</v>
+      </c>
+      <c r="L129" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" t="n">
+        <v>2</v>
+      </c>
+      <c r="N129" t="n">
+        <v>2</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2</v>
+      </c>
+      <c r="S129" t="n">
         <v>4</v>
       </c>
-      <c r="K129" t="n">
+      <c r="T129" t="n">
+        <v>6</v>
+      </c>
+      <c r="U129" t="n">
         <v>5</v>
       </c>
-      <c r="L129" t="n">
-        <v>9</v>
-      </c>
-      <c r="M129" t="n">
-        <v>2</v>
-      </c>
-      <c r="N129" t="n">
-        <v>4</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>4</v>
-      </c>
-      <c r="R129" t="n">
-        <v>2</v>
-      </c>
-      <c r="S129" t="n">
+      <c r="V129" t="n">
         <v>8</v>
       </c>
-      <c r="T129" t="n">
-        <v>10</v>
-      </c>
-      <c r="U129" t="n">
+      <c r="W129" t="n">
+        <v>21</v>
+      </c>
+      <c r="X129" t="n">
         <v>12</v>
       </c>
-      <c r="V129" t="n">
-        <v>12</v>
-      </c>
-      <c r="W129" t="n">
-        <v>18</v>
-      </c>
-      <c r="X129" t="n">
-        <v>17</v>
-      </c>
       <c r="Y129" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="Z129" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>Estadio Nuevo Arcángel</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>Avenida del Arcángel, Córdoba</t>
-        </is>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="n">
         <v>2</v>
       </c>
       <c r="AD129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="AF129" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AG129" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AI129" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AJ129" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AK129" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL129" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM129" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AN129" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="AO129" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AR129" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS129" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AT129" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AU129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW129" t="n">
         <v>0</v>
@@ -62445,16 +62477,16 @@
         <v>0</v>
       </c>
       <c r="BA129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB129" t="n">
-        <v>294</v>
+        <v>-1</v>
       </c>
       <c r="BC129" t="n">
         <v>0</v>
       </c>
       <c r="BD129" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="BE129" t="n">
         <v>0</v>
@@ -62469,187 +62501,187 @@
         <v>1</v>
       </c>
       <c r="BI129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ129" t="n">
         <v>3</v>
       </c>
       <c r="BK129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>115</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY129" t="n">
         <v>4</v>
       </c>
-      <c r="BO129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR129" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS129" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT129" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV129" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW129" t="n">
-        <v>40</v>
-      </c>
-      <c r="BX129" t="n">
-        <v>88</v>
-      </c>
-      <c r="BY129" t="n">
-        <v>84</v>
-      </c>
-      <c r="BZ129" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CA129" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CB129" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN129" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR129" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS129" t="n">
+      <c r="CZ129" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB129" t="n">
         <v>25</v>
       </c>
-      <c r="CT129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU129" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV129" t="n">
-        <v>18</v>
-      </c>
-      <c r="CW129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX129" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY129" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ129" t="n">
-        <v>55</v>
-      </c>
-      <c r="DA129" t="n">
-        <v>65</v>
-      </c>
-      <c r="DB129" t="n">
-        <v>35</v>
-      </c>
       <c r="DC129" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="DD129" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE129" t="n">
-        <v>0.75</v>
+        <v>1.86</v>
       </c>
       <c r="DF129" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DG129" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="DH129" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="DI129" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DJ129" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="DK129" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="DL129" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="DM129" t="n">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="DN129" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="DO129" t="n">
         <v>15</v>
       </c>
       <c r="DP129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR129" t="b">
         <v>0</v>
@@ -62667,101 +62699,69 @@
         <v>0</v>
       </c>
       <c r="DW129" t="n">
-        <v>26.22</v>
+        <v>18.47</v>
       </c>
       <c r="DX129" t="n">
-        <v>2.9</v>
+        <v>4.08</v>
       </c>
       <c r="DY129" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ129" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="EA129" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EB129" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EC129" t="inlineStr">
         <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="ED129" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EE129" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EF129" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="EG129" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EH129" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EI129" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="ED129" t="inlineStr"/>
+      <c r="EE129" t="inlineStr"/>
+      <c r="EF129" t="inlineStr"/>
+      <c r="EG129" t="inlineStr"/>
+      <c r="EH129" t="inlineStr"/>
+      <c r="EI129" t="inlineStr"/>
       <c r="EJ129" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EK129" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EL129" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EM129" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EN129" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EO129" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EP129" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EO129" t="inlineStr"/>
+      <c r="EP129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -64065,7 +64065,7 @@
         <v>1.38</v>
       </c>
       <c r="DE132" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF132" t="n">
         <v>1.33</v>
@@ -71265,7 +71265,7 @@
         <v>2</v>
       </c>
       <c r="DE147" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF147" t="n">
         <v>2.14</v>
@@ -71726,7 +71726,7 @@
         <v>55</v>
       </c>
       <c r="DD148" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE148" t="n">
         <v>1.63</v>
@@ -73153,7 +73153,7 @@
         <v>0.57</v>
       </c>
       <c r="DE151" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DF151" t="n">
         <v>0.67</v>
@@ -74570,7 +74570,7 @@
         <v>50</v>
       </c>
       <c r="DD154" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE154" t="n">
         <v>0.43</v>
@@ -75707,146 +75707,146 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F157" s="2" t="n">
         <v>45983.72916666666</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I157" t="n">
         <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" t="n">
+        <v>8</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2</v>
+      </c>
+      <c r="S157" t="n">
+        <v>15</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1</v>
+      </c>
+      <c r="U157" t="n">
+        <v>23</v>
+      </c>
+      <c r="V157" t="n">
+        <v>3</v>
+      </c>
+      <c r="W157" t="n">
+        <v>18</v>
+      </c>
+      <c r="X157" t="n">
         <v>10</v>
       </c>
-      <c r="R157" t="n">
-        <v>4</v>
-      </c>
-      <c r="S157" t="n">
-        <v>12</v>
-      </c>
-      <c r="T157" t="n">
-        <v>3</v>
-      </c>
-      <c r="U157" t="n">
-        <v>22</v>
-      </c>
-      <c r="V157" t="n">
-        <v>7</v>
-      </c>
-      <c r="W157" t="n">
-        <v>8</v>
-      </c>
-      <c r="X157" t="n">
-        <v>17</v>
-      </c>
       <c r="Y157" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="Z157" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque</t>
+          <t>Estadio Municipal de Ipurúa</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>Calle Arquitectura, Leganés</t>
+          <t>Calle de Ipurúa, Eibar</t>
         </is>
       </c>
       <c r="AC157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD157" t="n">
         <v>4</v>
       </c>
       <c r="AE157" t="n">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF157" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI157" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AJ157" t="n">
-        <v>3.5</v>
+        <v>4.93</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL157" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AM157" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AO157" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AR157" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AS157" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AT157" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AU157" t="n">
         <v>3</v>
       </c>
       <c r="AV157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW157" t="n">
         <v>1</v>
@@ -75855,22 +75855,22 @@
         <v>0</v>
       </c>
       <c r="AY157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB157" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="BC157" t="n">
         <v>0</v>
       </c>
       <c r="BD157" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="BE157" t="n">
         <v>0</v>
@@ -75885,178 +75885,178 @@
         <v>1</v>
       </c>
       <c r="BI157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ157" t="n">
         <v>0</v>
       </c>
       <c r="BK157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM157" t="n">
         <v>4</v>
       </c>
-      <c r="BL157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM157" t="n">
-        <v>1</v>
-      </c>
       <c r="BN157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO157" t="n">
         <v>4</v>
       </c>
-      <c r="BO157" t="n">
-        <v>0</v>
-      </c>
       <c r="BP157" t="n">
         <v>2</v>
       </c>
       <c r="BQ157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR157" t="n">
         <v>2</v>
       </c>
       <c r="BS157" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BT157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU157" t="n">
         <v>1</v>
       </c>
       <c r="BV157" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW157" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX157" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY157" t="n">
+        <v>62</v>
+      </c>
+      <c r="BZ157" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CA157" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CB157" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR157" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS157" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU157" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV157" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY157" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ157" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA157" t="n">
         <v>57</v>
       </c>
-      <c r="BW157" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX157" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY157" t="n">
-        <v>47</v>
-      </c>
-      <c r="BZ157" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CA157" t="n">
+      <c r="DB157" t="n">
+        <v>7</v>
+      </c>
+      <c r="DC157" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD157" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DE157" t="n">
         <v>0.88</v>
       </c>
-      <c r="CB157" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="CC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR157" t="n">
-        <v>23</v>
-      </c>
-      <c r="CS157" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU157" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV157" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX157" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY157" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ157" t="n">
-        <v>33</v>
-      </c>
-      <c r="DA157" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB157" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC157" t="n">
-        <v>83</v>
-      </c>
-      <c r="DD157" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DE157" t="n">
-        <v>1.5</v>
-      </c>
       <c r="DF157" t="n">
-        <v>0.83</v>
+        <v>2.14</v>
       </c>
       <c r="DG157" t="n">
-        <v>1.5</v>
+        <v>0.57</v>
       </c>
       <c r="DH157" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="DI157" t="n">
-        <v>1.92</v>
+        <v>0.64</v>
       </c>
       <c r="DJ157" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="DK157" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="DL157" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="DM157" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="DN157" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="DO157" t="n">
         <v>15</v>
@@ -76080,81 +76080,97 @@
         <v>0</v>
       </c>
       <c r="DV157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW157" t="n">
-        <v>7.24</v>
+        <v>6.63</v>
       </c>
       <c r="DX157" t="n">
-        <v>3.97</v>
+        <v>2.71</v>
       </c>
       <c r="DY157" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="DZ157" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA157" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EB157" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EC157" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="ED157" t="inlineStr">
         <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EE157" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EF157" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EG157" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EH157" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI157" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EJ157" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EK157" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="EL157" t="inlineStr">
+        <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="EE157" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EF157" t="inlineStr"/>
-      <c r="EG157" t="inlineStr"/>
-      <c r="EH157" t="inlineStr"/>
-      <c r="EI157" t="inlineStr"/>
-      <c r="EJ157" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="EK157" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="EL157" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
       <c r="EM157" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EN157" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EO157" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EP157" t="inlineStr">
@@ -76179,146 +76195,146 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F158" s="2" t="n">
         <v>45983.72916666666</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
         <v>3</v>
       </c>
       <c r="J158" t="n">
+        <v>5</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>5</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>10</v>
+      </c>
+      <c r="R158" t="n">
+        <v>4</v>
+      </c>
+      <c r="S158" t="n">
+        <v>12</v>
+      </c>
+      <c r="T158" t="n">
+        <v>3</v>
+      </c>
+      <c r="U158" t="n">
+        <v>22</v>
+      </c>
+      <c r="V158" t="n">
         <v>7</v>
       </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>7</v>
-      </c>
-      <c r="M158" t="n">
-        <v>6</v>
-      </c>
-      <c r="N158" t="n">
-        <v>3</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q158" t="n">
+      <c r="W158" t="n">
         <v>8</v>
       </c>
-      <c r="R158" t="n">
-        <v>2</v>
-      </c>
-      <c r="S158" t="n">
-        <v>15</v>
-      </c>
-      <c r="T158" t="n">
-        <v>1</v>
-      </c>
-      <c r="U158" t="n">
-        <v>23</v>
-      </c>
-      <c r="V158" t="n">
-        <v>3</v>
-      </c>
-      <c r="W158" t="n">
-        <v>18</v>
-      </c>
       <c r="X158" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Y158" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Z158" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Ipurúa</t>
+          <t>Estadio Municipal de Butarque</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>Calle de Ipurúa, Eibar</t>
+          <t>Calle Arquitectura, Leganés</t>
         </is>
       </c>
       <c r="AC158" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD158" t="n">
         <v>4</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AF158" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AG158" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI158" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="AJ158" t="n">
-        <v>4.93</v>
+        <v>3.5</v>
       </c>
       <c r="AK158" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AL158" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AN158" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AO158" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AR158" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AS158" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AT158" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AU158" t="n">
         <v>3</v>
       </c>
       <c r="AV158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW158" t="n">
         <v>1</v>
@@ -76327,22 +76343,22 @@
         <v>0</v>
       </c>
       <c r="AY158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB158" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="BC158" t="n">
         <v>0</v>
       </c>
       <c r="BD158" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="BE158" t="n">
         <v>0</v>
@@ -76357,178 +76373,178 @@
         <v>1</v>
       </c>
       <c r="BI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK158" t="n">
         <v>4</v>
       </c>
-      <c r="BJ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK158" t="n">
-        <v>3</v>
-      </c>
       <c r="BL158" t="n">
         <v>0</v>
       </c>
       <c r="BM158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN158" t="n">
         <v>4</v>
       </c>
-      <c r="BN158" t="n">
-        <v>3</v>
-      </c>
       <c r="BO158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP158" t="n">
         <v>2</v>
       </c>
       <c r="BQ158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR158" t="n">
         <v>2</v>
       </c>
       <c r="BS158" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BT158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU158" t="n">
         <v>1</v>
       </c>
       <c r="BV158" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="BW158" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX158" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY158" t="n">
+        <v>47</v>
+      </c>
+      <c r="BZ158" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CA158" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB158" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR158" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS158" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU158" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV158" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX158" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY158" t="n">
         <v>12</v>
       </c>
-      <c r="BX158" t="n">
+      <c r="CZ158" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA158" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB158" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC158" t="n">
         <v>83</v>
       </c>
-      <c r="BY158" t="n">
-        <v>62</v>
-      </c>
-      <c r="BZ158" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CA158" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="CB158" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR158" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS158" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU158" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV158" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY158" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ158" t="n">
-        <v>36</v>
-      </c>
-      <c r="DA158" t="n">
-        <v>57</v>
-      </c>
-      <c r="DB158" t="n">
-        <v>7</v>
-      </c>
-      <c r="DC158" t="n">
-        <v>57</v>
-      </c>
       <c r="DD158" t="n">
-        <v>1.88</v>
+        <v>0.71</v>
       </c>
       <c r="DE158" t="n">
-        <v>0.88</v>
+        <v>1.5</v>
       </c>
       <c r="DF158" t="n">
-        <v>2.14</v>
+        <v>0.83</v>
       </c>
       <c r="DG158" t="n">
-        <v>0.57</v>
+        <v>1.5</v>
       </c>
       <c r="DH158" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="DI158" t="n">
-        <v>0.64</v>
+        <v>1.92</v>
       </c>
       <c r="DJ158" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="DK158" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="DL158" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="DM158" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DN158" t="n">
-        <v>3.22</v>
+        <v>2.71</v>
       </c>
       <c r="DO158" t="n">
         <v>15</v>
@@ -76552,97 +76568,81 @@
         <v>0</v>
       </c>
       <c r="DV158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW158" t="n">
-        <v>6.63</v>
+        <v>7.24</v>
       </c>
       <c r="DX158" t="n">
-        <v>2.71</v>
+        <v>3.97</v>
       </c>
       <c r="DY158" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ158" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="EA158" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EB158" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EC158" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="ED158" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EE158" t="inlineStr">
         <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EF158" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EG158" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EH158" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EI158" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EF158" t="inlineStr"/>
+      <c r="EG158" t="inlineStr"/>
+      <c r="EH158" t="inlineStr"/>
+      <c r="EI158" t="inlineStr"/>
       <c r="EJ158" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EK158" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EL158" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EM158" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EN158" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EO158" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EP158" t="inlineStr">
@@ -80354,7 +80354,7 @@
         <v>85</v>
       </c>
       <c r="DD166" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DE166" t="n">
         <v>1.5</v>
@@ -80968,6 +80968,942 @@
       <c r="EP167" t="inlineStr">
         <is>
           <t>2.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Spain_Segunda_División_2025-2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>16</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Ceuta</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>45990.54166666666</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>10</v>
+      </c>
+      <c r="K168" t="n">
+        <v>7</v>
+      </c>
+      <c r="L168" t="n">
+        <v>17</v>
+      </c>
+      <c r="M168" t="n">
+        <v>5</v>
+      </c>
+      <c r="N168" t="n">
+        <v>3</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>5</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1</v>
+      </c>
+      <c r="S168" t="n">
+        <v>9</v>
+      </c>
+      <c r="T168" t="n">
+        <v>8</v>
+      </c>
+      <c r="U168" t="n">
+        <v>14</v>
+      </c>
+      <c r="V168" t="n">
+        <v>9</v>
+      </c>
+      <c r="W168" t="n">
+        <v>21</v>
+      </c>
+      <c r="X168" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>10870</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV168" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW168" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX168" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY168" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ168" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CA168" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="CB168" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR168" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS168" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU168" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV168" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW168" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX168" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY168" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ168" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA168" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB168" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC168" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD168" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DE168" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DF168" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DG168" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DI168" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ168" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK168" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL168" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM168" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DN168" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DO168" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP168" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV168" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW168" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="DX168" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="DY168" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="DZ168" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="EA168" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EB168" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EC168" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="ED168" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EE168" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EF168" t="inlineStr"/>
+      <c r="EG168" t="inlineStr"/>
+      <c r="EH168" t="inlineStr"/>
+      <c r="EI168" t="inlineStr"/>
+      <c r="EJ168" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EK168" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EL168" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EM168" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EN168" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EO168" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EP168" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Spain_Segunda_División_2025-2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>16</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Cultural y Deportiva Leonesa</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>45990.63541666666</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>4</v>
+      </c>
+      <c r="K169" t="n">
+        <v>4</v>
+      </c>
+      <c r="L169" t="n">
+        <v>8</v>
+      </c>
+      <c r="M169" t="n">
+        <v>2</v>
+      </c>
+      <c r="N169" t="n">
+        <v>3</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>4</v>
+      </c>
+      <c r="R169" t="n">
+        <v>3</v>
+      </c>
+      <c r="S169" t="n">
+        <v>6</v>
+      </c>
+      <c r="T169" t="n">
+        <v>5</v>
+      </c>
+      <c r="U169" t="n">
+        <v>10</v>
+      </c>
+      <c r="V169" t="n">
+        <v>8</v>
+      </c>
+      <c r="W169" t="n">
+        <v>11</v>
+      </c>
+      <c r="X169" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Reino de León</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>Paseo Sáenz de Miera, León</t>
+        </is>
+      </c>
+      <c r="AC169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>282</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV169" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW169" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX169" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY169" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ169" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB169" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR169" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS169" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU169" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV169" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX169" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY169" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ169" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA169" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB169" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC169" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD169" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE169" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF169" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG169" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI169" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DJ169" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK169" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL169" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DM169" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DN169" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DO169" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP169" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV169" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW169" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="DX169" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DY169" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="DZ169" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="EA169" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EB169" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EC169" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="ED169" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EE169" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EF169" t="inlineStr"/>
+      <c r="EG169" t="inlineStr"/>
+      <c r="EH169" t="inlineStr"/>
+      <c r="EI169" t="inlineStr"/>
+      <c r="EJ169" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EK169" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EL169" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EM169" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EN169" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EO169" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EP169" t="inlineStr">
+        <is>
+          <t>2.27</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
@@ -82963,13 +82963,13 @@
         <v>3</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T172" t="n">
         <v>2</v>
       </c>
       <c r="U172" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V172" t="n">
         <v>5</v>
@@ -83144,13 +83144,13 @@
         <v>105</v>
       </c>
       <c r="BZ172" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="CA172" t="n">
         <v>1.1</v>
       </c>
       <c r="CB172" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="CC172" t="n">
         <v>0</v>
@@ -84398,13 +84398,13 @@
         <v>11</v>
       </c>
       <c r="T175" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U175" t="n">
         <v>16</v>
       </c>
       <c r="V175" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W175" t="n">
         <v>15</v>
@@ -84579,10 +84579,10 @@
         <v>1.71</v>
       </c>
       <c r="CA175" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="CB175" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="CC175" t="n">
         <v>0</v>
@@ -84901,10 +84901,10 @@
         <v>22</v>
       </c>
       <c r="Y176" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z176" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA176" t="inlineStr">
         <is>

--- a/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
+++ b/data/matches/leagues/Spain_Segunda_División_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP188" headerRowCount="1">
-  <autoFilter ref="A1:EP188"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP189" headerRowCount="1">
+  <autoFilter ref="A1:EP189"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP188"/>
+  <dimension ref="A1:EP189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -8581,7 +8581,7 @@
         <v>0.88</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -10486,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE20" t="n">
         <v>1.67</v>
@@ -20137,7 +20137,7 @@
         <v>2.25</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF40" t="n">
         <v>0</v>
@@ -22038,7 +22038,7 @@
         <v>0</v>
       </c>
       <c r="DD44" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE44" t="n">
         <v>1.44</v>
@@ -28181,7 +28181,7 @@
         <v>1.88</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -28666,7 +28666,7 @@
         <v>50</v>
       </c>
       <c r="DD58" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE58" t="n">
         <v>1.56</v>
@@ -43534,7 +43534,7 @@
         <v>54</v>
       </c>
       <c r="DD89" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE89" t="n">
         <v>1.33</v>
@@ -47373,7 +47373,7 @@
         <v>1.56</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF97" t="n">
         <v>2.5</v>
@@ -54482,7 +54482,7 @@
         <v>43</v>
       </c>
       <c r="DD112" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE112" t="n">
         <v>0.78</v>
@@ -55603,40 +55603,40 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45955.6875</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K115" t="n">
+        <v>3</v>
+      </c>
+      <c r="L115" t="n">
+        <v>9</v>
+      </c>
+      <c r="M115" t="n">
         <v>4</v>
       </c>
-      <c r="L115" t="n">
-        <v>12</v>
-      </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -55645,101 +55645,101 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
         <v>1</v>
       </c>
       <c r="S115" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T115" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="W115" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X115" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y115" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="Z115" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Estadio Nuevo Los Cármenes</t>
+          <t>Estadio Municipal de El Plantío</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Calle Pintor Manuel Maldonado, Granada</t>
+          <t>Calle del Dos de Mayo, Burgos</t>
         </is>
       </c>
       <c r="AC115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE115" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK115" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF115" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH115" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK115" t="n">
-        <v>2</v>
-      </c>
       <c r="AL115" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AU115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV115" t="n">
         <v>0</v>
@@ -55748,25 +55748,25 @@
         <v>0</v>
       </c>
       <c r="AX115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY115" t="n">
         <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA115" t="n">
         <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>-1</v>
+        <v>4546</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55781,37 +55781,37 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BL115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM115" t="n">
         <v>5</v>
       </c>
       <c r="BN115" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BO115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BT115" t="n">
         <v>3</v>
@@ -55820,34 +55820,34 @@
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="BW115" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BX115" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="BY115" t="n">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="BZ115" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="CA115" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="CC115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD115" t="n">
         <v>0</v>
       </c>
       <c r="CE115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF115" t="n">
         <v>0</v>
@@ -55871,10 +55871,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55889,76 +55889,76 @@
         <v>24</v>
       </c>
       <c r="CS115" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CV115" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CZ115" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>68</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>58</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ115" t="n">
         <v>43</v>
       </c>
-      <c r="DA115" t="n">
-        <v>65</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>23</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>68</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DH115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI115" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DJ115" t="n">
-        <v>58</v>
-      </c>
       <c r="DK115" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="DM115" t="n">
-        <v>0.98</v>
+        <v>1.19</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="DO115" t="n">
         <v>17</v>
       </c>
       <c r="DP115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ115" t="b">
         <v>0</v>
@@ -55979,91 +55979,91 @@
         <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>25.8</v>
+        <v>12.02</v>
       </c>
       <c r="DX115" t="n">
-        <v>2.62</v>
+        <v>4.53</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="ED115" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EE115" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EF115" t="inlineStr"/>
       <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EN115" t="inlineStr">
+        <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="EI115" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="EJ115" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="EL115" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EM115" t="inlineStr">
+      <c r="EO115" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="EN115" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EO115" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -56083,40 +56083,40 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45955.6875</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L116" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -56125,101 +56125,101 @@
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
         <v>1</v>
       </c>
       <c r="S116" t="n">
+        <v>17</v>
+      </c>
+      <c r="T116" t="n">
+        <v>10</v>
+      </c>
+      <c r="U116" t="n">
+        <v>18</v>
+      </c>
+      <c r="V116" t="n">
         <v>11</v>
       </c>
-      <c r="T116" t="n">
-        <v>4</v>
-      </c>
-      <c r="U116" t="n">
-        <v>14</v>
-      </c>
-      <c r="V116" t="n">
-        <v>5</v>
-      </c>
       <c r="W116" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X116" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y116" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Z116" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Estadio Municipal de El Plantío</t>
+          <t>Estadio Nuevo Los Cármenes</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>Calle del Dos de Mayo, Burgos</t>
+          <t>Calle Pintor Manuel Maldonado, Granada</t>
         </is>
       </c>
       <c r="AC116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE116" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM116" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF116" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG116" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AH116" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI116" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AK116" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL116" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM116" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AN116" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AO116" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AP116" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ116" t="n">
         <v>1.45</v>
       </c>
-      <c r="AQ116" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR116" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AU116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV116" t="n">
         <v>0</v>
@@ -56228,25 +56228,25 @@
         <v>0</v>
       </c>
       <c r="AX116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY116" t="n">
         <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA116" t="n">
         <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>4546</v>
+        <v>-1</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56261,37 +56261,37 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BJ116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BL116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM116" t="n">
         <v>5</v>
       </c>
       <c r="BN116" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT116" t="n">
         <v>3</v>
@@ -56300,34 +56300,34 @@
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="BW116" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BX116" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="BY116" t="n">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="BZ116" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CA116" t="n">
-        <v>0.59</v>
+        <v>0.96</v>
       </c>
       <c r="CB116" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="CC116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD116" t="n">
         <v>0</v>
       </c>
       <c r="CE116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF116" t="n">
         <v>0</v>
@@ -56351,10 +56351,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56369,76 +56369,76 @@
         <v>24</v>
       </c>
       <c r="CS116" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CV116" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY116" t="n">
         <v>13</v>
       </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY116" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ116" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>23</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ116" t="n">
         <v>58</v>
       </c>
-      <c r="DA116" t="n">
-        <v>68</v>
-      </c>
-      <c r="DB116" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC116" t="n">
-        <v>58</v>
-      </c>
-      <c r="DD116" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF116" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH116" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ116" t="n">
-        <v>43</v>
-      </c>
       <c r="DK116" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.19</v>
+        <v>0.98</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DO116" t="n">
         <v>17</v>
       </c>
       <c r="DP116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ116" t="b">
         <v>0</v>
@@ -56459,91 +56459,91 @@
         <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>12.02</v>
+        <v>25.8</v>
       </c>
       <c r="DX116" t="n">
-        <v>4.53</v>
+        <v>2.62</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="ED116" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EE116" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EF116" t="inlineStr"/>
       <c r="EG116" t="inlineStr"/>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EK116" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="EL116" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EM116" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN116" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -57539,12 +57539,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
@@ -57560,141 +57560,141 @@
         <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K119" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L119" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M119" t="n">
         <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S119" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T119" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="U119" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="V119" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="W119" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X119" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y119" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="Z119" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AA119" t="inlineStr"/>
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AF119" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG119" t="n">
         <v>3.3</v>
       </c>
-      <c r="AG119" t="n">
-        <v>5</v>
-      </c>
       <c r="AH119" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AI119" t="n">
-        <v>2.09</v>
+        <v>1.59</v>
       </c>
       <c r="AJ119" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK119" t="n">
-        <v>2.01</v>
+        <v>1.51</v>
       </c>
       <c r="AL119" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN119" t="n">
         <v>1.75</v>
       </c>
-      <c r="AM119" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN119" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AO119" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR119" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AS119" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AU119" t="n">
         <v>1</v>
       </c>
       <c r="AV119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY119" t="n">
         <v>0</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="BC119" t="n">
         <v>0</v>
       </c>
       <c r="BD119" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BE119" t="n">
         <v>0</v>
@@ -57709,178 +57709,178 @@
         <v>1</v>
       </c>
       <c r="BI119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM119" t="n">
         <v>4</v>
       </c>
-      <c r="BK119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL119" t="n">
+      <c r="BN119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU119" t="n">
         <v>11</v>
       </c>
-      <c r="BM119" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN119" t="n">
+      <c r="CV119" t="n">
         <v>11</v>
       </c>
-      <c r="BO119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT119" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV119" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW119" t="n">
+      <c r="CW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX119" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY119" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ119" t="n">
         <v>80</v>
       </c>
-      <c r="BX119" t="n">
-        <v>77</v>
-      </c>
-      <c r="BY119" t="n">
-        <v>107</v>
-      </c>
-      <c r="BZ119" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="CA119" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CB119" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="CC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI119" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ119" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN119" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP119" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ119" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR119" t="n">
-        <v>23</v>
-      </c>
-      <c r="CS119" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT119" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU119" t="n">
-        <v>18</v>
-      </c>
-      <c r="CV119" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW119" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX119" t="n">
-        <v>13</v>
-      </c>
-      <c r="CY119" t="n">
-        <v>5</v>
-      </c>
-      <c r="CZ119" t="n">
-        <v>50</v>
-      </c>
       <c r="DA119" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="DB119" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="DC119" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.89</v>
+        <v>1.56</v>
       </c>
       <c r="DF119" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DG119" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DH119" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ119" t="n">
+        <v>20</v>
+      </c>
+      <c r="DK119" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL119" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DM119" t="n">
         <v>1.5</v>
       </c>
-      <c r="DI119" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DJ119" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK119" t="n">
-        <v>40</v>
-      </c>
-      <c r="DL119" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DM119" t="n">
-        <v>1.37</v>
-      </c>
       <c r="DN119" t="n">
-        <v>3.1</v>
+        <v>4.06</v>
       </c>
       <c r="DO119" t="n">
         <v>17</v>
@@ -57907,99 +57907,83 @@
         <v>0</v>
       </c>
       <c r="DW119" t="n">
-        <v>14.98</v>
+        <v>23.27</v>
       </c>
       <c r="DX119" t="n">
-        <v>2.04</v>
+        <v>5.18</v>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC119" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EE119" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EF119" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
-      <c r="EG119" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EH119" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EI119" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF119" t="inlineStr"/>
+      <c r="EG119" t="inlineStr"/>
+      <c r="EH119" t="inlineStr"/>
+      <c r="EI119" t="inlineStr"/>
       <c r="EJ119" t="inlineStr">
         <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EK119" t="inlineStr">
+        <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="EK119" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
       <c r="EL119" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM119" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EN119" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EO119" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EP119" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.52</t>
         </is>
       </c>
     </row>
@@ -58019,12 +58003,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
@@ -58040,141 +58024,141 @@
         <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L120" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M120" t="n">
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
+        <v>3</v>
+      </c>
+      <c r="R120" t="n">
+        <v>3</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="n">
+        <v>19</v>
+      </c>
+      <c r="U120" t="n">
         <v>4</v>
       </c>
-      <c r="R120" t="n">
-        <v>4</v>
-      </c>
-      <c r="S120" t="n">
-        <v>11</v>
-      </c>
-      <c r="T120" t="n">
-        <v>5</v>
-      </c>
-      <c r="U120" t="n">
-        <v>15</v>
-      </c>
       <c r="V120" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="W120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X120" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y120" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="Z120" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AF120" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AG120" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AH120" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AI120" t="n">
-        <v>1.59</v>
+        <v>2.09</v>
       </c>
       <c r="AJ120" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AK120" t="n">
-        <v>1.51</v>
+        <v>2.01</v>
       </c>
       <c r="AL120" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AO120" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR120" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AS120" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="AU120" t="n">
         <v>1</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY120" t="n">
         <v>0</v>
       </c>
       <c r="AZ120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB120" t="n">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="BC120" t="n">
         <v>0</v>
       </c>
       <c r="BD120" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="BE120" t="n">
         <v>0</v>
@@ -58189,178 +58173,178 @@
         <v>1</v>
       </c>
       <c r="BI120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL120" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="BM120" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BN120" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU120" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV120" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX120" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY120" t="n">
         <v>5</v>
       </c>
-      <c r="BO120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS120" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV120" t="n">
-        <v>35</v>
-      </c>
-      <c r="BW120" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX120" t="n">
-        <v>108</v>
-      </c>
-      <c r="BY120" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ120" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA120" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CB120" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="CC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI120" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ120" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM120" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP120" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ120" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR120" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS120" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT120" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU120" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV120" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW120" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX120" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY120" t="n">
-        <v>11</v>
-      </c>
       <c r="CZ120" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="DA120" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="DB120" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="DC120" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="DD120" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.56</v>
+        <v>0.89</v>
       </c>
       <c r="DF120" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="DG120" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="DH120" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DI120" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="DJ120" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="DK120" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="DL120" t="n">
-        <v>2.56</v>
+        <v>1.73</v>
       </c>
       <c r="DM120" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="DN120" t="n">
-        <v>4.06</v>
+        <v>3.1</v>
       </c>
       <c r="DO120" t="n">
         <v>17</v>
@@ -58387,83 +58371,99 @@
         <v>0</v>
       </c>
       <c r="DW120" t="n">
-        <v>23.27</v>
+        <v>14.98</v>
       </c>
       <c r="DX120" t="n">
-        <v>5.18</v>
+        <v>2.04</v>
       </c>
       <c r="DY120" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="DZ120" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="EA120" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EB120" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EC120" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="ED120" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EE120" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EF120" t="inlineStr"/>
-      <c r="EG120" t="inlineStr"/>
-      <c r="EH120" t="inlineStr"/>
-      <c r="EI120" t="inlineStr"/>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EF120" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EH120" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI120" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
       <c r="EJ120" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EK120" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="EL120" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EM120" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EN120" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EO120" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EP120" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
@@ -59770,7 +59770,7 @@
         <v>62</v>
       </c>
       <c r="DD123" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE123" t="n">
         <v>1</v>
@@ -59939,170 +59939,170 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
         <v>45962.72916666666</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
         <v>3</v>
       </c>
       <c r="J124" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K124" t="n">
+        <v>7</v>
+      </c>
+      <c r="L124" t="n">
+        <v>14</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>6</v>
+      </c>
+      <c r="R124" t="n">
         <v>4</v>
       </c>
-      <c r="L124" t="n">
+      <c r="S124" t="n">
+        <v>8</v>
+      </c>
+      <c r="T124" t="n">
+        <v>17</v>
+      </c>
+      <c r="U124" t="n">
+        <v>14</v>
+      </c>
+      <c r="V124" t="n">
+        <v>21</v>
+      </c>
+      <c r="W124" t="n">
         <v>13</v>
       </c>
-      <c r="M124" t="n">
-        <v>3</v>
-      </c>
-      <c r="N124" t="n">
-        <v>3</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>3</v>
-      </c>
-      <c r="R124" t="n">
-        <v>2</v>
-      </c>
-      <c r="S124" t="n">
-        <v>10</v>
-      </c>
-      <c r="T124" t="n">
-        <v>4</v>
-      </c>
-      <c r="U124" t="n">
-        <v>13</v>
-      </c>
-      <c r="V124" t="n">
+      <c r="X124" t="n">
         <v>6</v>
       </c>
-      <c r="W124" t="n">
-        <v>17</v>
-      </c>
-      <c r="X124" t="n">
-        <v>17</v>
-      </c>
       <c r="Y124" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="Z124" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque</t>
+          <t>Estadio Carlos Belmonte</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Calle Arquitectura, Leganés</t>
+          <t>Avenida de España, Albacete</t>
         </is>
       </c>
       <c r="AC124" t="n">
         <v>3</v>
       </c>
       <c r="AD124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AF124" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AG124" t="n">
-        <v>3.92</v>
+        <v>3.79</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AI124" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS124" t="n">
         <v>2.45</v>
       </c>
-      <c r="AJ124" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AK124" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AL124" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM124" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN124" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AO124" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AP124" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ124" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR124" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS124" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AT124" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AU124" t="n">
         <v>3</v>
       </c>
       <c r="AV124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY124" t="n">
         <v>0</v>
       </c>
       <c r="AZ124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB124" t="n">
-        <v>4546</v>
+        <v>316</v>
       </c>
       <c r="BC124" t="n">
         <v>0</v>
       </c>
       <c r="BD124" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="BE124" t="n">
         <v>0</v>
@@ -60117,178 +60117,178 @@
         <v>1</v>
       </c>
       <c r="BI124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM124" t="n">
         <v>7</v>
       </c>
-      <c r="BJ124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK124" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL124" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM124" t="n">
-        <v>8</v>
-      </c>
       <c r="BN124" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY124" t="n">
         <v>5</v>
       </c>
-      <c r="BO124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP124" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ124" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS124" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT124" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV124" t="n">
+      <c r="CZ124" t="n">
         <v>55</v>
       </c>
-      <c r="BW124" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX124" t="n">
-        <v>88</v>
-      </c>
-      <c r="BY124" t="n">
-        <v>68</v>
-      </c>
-      <c r="BZ124" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CA124" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="CB124" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR124" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS124" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU124" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV124" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX124" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY124" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ124" t="n">
-        <v>50</v>
-      </c>
       <c r="DA124" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="DB124" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="DC124" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="DD124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG124" t="n">
         <v>0.75</v>
       </c>
-      <c r="DE124" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DF124" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG124" t="n">
+      <c r="DH124" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI124" t="n">
         <v>1.4</v>
       </c>
-      <c r="DH124" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DI124" t="n">
-        <v>1.64</v>
-      </c>
       <c r="DJ124" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DK124" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="DL124" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="DM124" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
       <c r="DN124" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="DO124" t="n">
         <v>17</v>
@@ -60315,91 +60315,91 @@
         <v>1</v>
       </c>
       <c r="DW124" t="n">
-        <v>14.8</v>
+        <v>19.22</v>
       </c>
       <c r="DX124" t="n">
-        <v>6.8</v>
+        <v>7.18</v>
       </c>
       <c r="DY124" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ124" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EC124" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="ED124" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EE124" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EF124" t="inlineStr"/>
       <c r="EG124" t="inlineStr"/>
       <c r="EH124" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EI124" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EJ124" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EK124" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="EL124" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EM124" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EN124" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EO124" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EP124" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.34</t>
         </is>
       </c>
     </row>
@@ -60419,40 +60419,40 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
         <v>45962.72916666666</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I125" t="n">
         <v>3</v>
       </c>
       <c r="J125" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K125" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L125" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M125" t="n">
         <v>3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -60461,128 +60461,128 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
+        <v>3</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="n">
+        <v>4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>13</v>
+      </c>
+      <c r="V125" t="n">
         <v>6</v>
       </c>
-      <c r="R125" t="n">
-        <v>4</v>
-      </c>
-      <c r="S125" t="n">
-        <v>8</v>
-      </c>
-      <c r="T125" t="n">
+      <c r="W125" t="n">
         <v>17</v>
       </c>
-      <c r="U125" t="n">
-        <v>14</v>
-      </c>
-      <c r="V125" t="n">
-        <v>21</v>
-      </c>
-      <c r="W125" t="n">
-        <v>13</v>
-      </c>
       <c r="X125" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Y125" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="Z125" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Calle Arquitectura, Leganés</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>4546</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
         <v>60</v>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>Estadio Carlos Belmonte</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>Avenida de España, Albacete</t>
-        </is>
-      </c>
-      <c r="AC125" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT125" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AU125" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ125" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA125" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB125" t="n">
-        <v>316</v>
-      </c>
-      <c r="BC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD125" t="n">
-        <v>43</v>
       </c>
       <c r="BE125" t="n">
         <v>0</v>
@@ -60597,37 +60597,37 @@
         <v>1</v>
       </c>
       <c r="BI125" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BJ125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN125" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BO125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT125" t="n">
         <v>3</v>
@@ -60636,25 +60636,25 @@
         <v>1</v>
       </c>
       <c r="BV125" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BW125" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="BX125" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="BY125" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="BZ125" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="CA125" t="n">
-        <v>1.99</v>
+        <v>0.71</v>
       </c>
       <c r="CB125" t="n">
-        <v>3.59</v>
+        <v>2.14</v>
       </c>
       <c r="CC125" t="n">
         <v>0</v>
@@ -60681,16 +60681,16 @@
         <v>1</v>
       </c>
       <c r="CK125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO125" t="n">
         <v>0</v>
@@ -60702,73 +60702,73 @@
         <v>1</v>
       </c>
       <c r="CR125" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CS125" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CT125" t="n">
         <v>1</v>
       </c>
       <c r="CU125" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
         <v>6</v>
       </c>
-      <c r="CV125" t="n">
+      <c r="CY125" t="n">
         <v>13</v>
       </c>
-      <c r="CW125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX125" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY125" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ125" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="DA125" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="DB125" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="DC125" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.5</v>
+        <v>1.63</v>
       </c>
       <c r="DF125" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DG125" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="DH125" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM125" t="n">
         <v>1.18</v>
       </c>
-      <c r="DI125" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ125" t="n">
-        <v>45</v>
-      </c>
-      <c r="DK125" t="n">
-        <v>35</v>
-      </c>
-      <c r="DL125" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="DM125" t="n">
-        <v>0.72</v>
-      </c>
       <c r="DN125" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="DO125" t="n">
         <v>17</v>
@@ -60795,91 +60795,91 @@
         <v>1</v>
       </c>
       <c r="DW125" t="n">
-        <v>19.22</v>
+        <v>14.8</v>
       </c>
       <c r="DX125" t="n">
-        <v>7.18</v>
+        <v>6.8</v>
       </c>
       <c r="DY125" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ125" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA125" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EB125" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EC125" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="ED125" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE125" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EF125" t="inlineStr"/>
       <c r="EG125" t="inlineStr"/>
       <c r="EH125" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EI125" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EJ125" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EK125" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="EL125" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EM125" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EN125" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EO125" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EP125" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -64537,7 +64537,7 @@
         <v>2</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF133" t="n">
         <v>1.8</v>
@@ -69967,37 +69967,37 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
         <v>45976.625</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J145" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L145" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N145" t="n">
         <v>1</v>
@@ -70009,128 +70009,128 @@
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R145" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S145" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T145" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U145" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V145" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W145" t="n">
         <v>9</v>
       </c>
       <c r="X145" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Y145" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="Z145" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Estadio Carlos Belmonte</t>
+          <t>Nou Estadi Castalia</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>Avenida de España, Albacete</t>
+          <t>Calle de Huesca, Castellón de la Plana</t>
         </is>
       </c>
       <c r="AC145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD145" t="n">
         <v>1</v>
       </c>
       <c r="AE145" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AF145" t="n">
-        <v>3.48</v>
+        <v>5.2</v>
       </c>
       <c r="AG145" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AH145" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AI145" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AJ145" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="AK145" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AL145" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="AM145" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AN145" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AO145" t="n">
         <v>2.31</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AR145" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="AS145" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="AT145" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AU145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AV145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX145" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ145" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BA145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB145" t="n">
-        <v>316</v>
+        <v>6257</v>
       </c>
       <c r="BC145" t="n">
         <v>0</v>
       </c>
       <c r="BD145" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="BE145" t="n">
         <v>0</v>
@@ -70145,73 +70145,73 @@
         <v>1</v>
       </c>
       <c r="BI145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BJ145" t="n">
         <v>0</v>
       </c>
       <c r="BK145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BN145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP145" t="n">
         <v>1</v>
       </c>
       <c r="BQ145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR145" t="n">
         <v>0</v>
       </c>
       <c r="BS145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU145" t="n">
         <v>1</v>
       </c>
       <c r="BV145" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="BW145" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BX145" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="BY145" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="BZ145" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="CA145" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="CB145" t="n">
-        <v>3.61</v>
+        <v>4.45</v>
       </c>
       <c r="CC145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD145" t="n">
         <v>0</v>
       </c>
       <c r="CE145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF145" t="n">
         <v>0</v>
@@ -70235,7 +70235,7 @@
         <v>0</v>
       </c>
       <c r="CM145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN145" t="n">
         <v>0</v>
@@ -70244,22 +70244,22 @@
         <v>0</v>
       </c>
       <c r="CP145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ145" t="n">
         <v>1</v>
       </c>
       <c r="CR145" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="CS145" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="CT145" t="n">
         <v>1</v>
       </c>
       <c r="CU145" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CV145" t="n">
         <v>9</v>
@@ -70268,55 +70268,55 @@
         <v>1</v>
       </c>
       <c r="CX145" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CY145" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CZ145" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="DA145" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="DB145" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="DC145" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="DE145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF145" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="DG145" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="DH145" t="n">
         <v>1.23</v>
       </c>
       <c r="DI145" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="DJ145" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="DK145" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="DL145" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="DM145" t="n">
-        <v>1.54</v>
+        <v>1.1</v>
       </c>
       <c r="DN145" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="DO145" t="n">
         <v>17</v>
@@ -70325,117 +70325,117 @@
         <v>1</v>
       </c>
       <c r="DQ145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW145" t="n">
-        <v>13.45</v>
+        <v>19.95</v>
       </c>
       <c r="DX145" t="n">
-        <v>7.04</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DY145" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ145" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="EA145" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="EB145" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EC145" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="ED145" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EE145" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF145" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EG145" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EH145" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EI145" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EJ145" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="EK145" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="EL145" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EM145" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN145" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EO145" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EP145" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -70455,37 +70455,37 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
         <v>45976.625</v>
       </c>
       <c r="G146" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="n">
         <v>4</v>
       </c>
-      <c r="I146" t="n">
-        <v>9</v>
-      </c>
-      <c r="J146" t="n">
-        <v>14</v>
-      </c>
       <c r="K146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L146" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N146" t="n">
         <v>1</v>
@@ -70497,128 +70497,128 @@
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R146" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U146" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V146" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W146" t="n">
         <v>9</v>
       </c>
       <c r="X146" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y146" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="Z146" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>Nou Estadi Castalia</t>
+          <t>Estadio Carlos Belmonte</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>Calle de Huesca, Castellón de la Plana</t>
+          <t>Avenida de España, Albacete</t>
         </is>
       </c>
       <c r="AC146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD146" t="n">
         <v>1</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AF146" t="n">
-        <v>5.2</v>
+        <v>3.48</v>
       </c>
       <c r="AG146" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AH146" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AI146" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AJ146" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="AK146" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AL146" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="AM146" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AN146" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AO146" t="n">
         <v>2.31</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AR146" t="n">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="AS146" t="n">
-        <v>3.29</v>
+        <v>2.94</v>
       </c>
       <c r="AT146" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AU146" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AV146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX146" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ146" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BA146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB146" t="n">
-        <v>6257</v>
+        <v>316</v>
       </c>
       <c r="BC146" t="n">
         <v>0</v>
       </c>
       <c r="BD146" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="BE146" t="n">
         <v>0</v>
@@ -70633,73 +70633,73 @@
         <v>1</v>
       </c>
       <c r="BI146" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BJ146" t="n">
         <v>0</v>
       </c>
       <c r="BK146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN146" t="n">
         <v>5</v>
       </c>
-      <c r="BL146" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM146" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN146" t="n">
-        <v>6</v>
-      </c>
       <c r="BO146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP146" t="n">
         <v>1</v>
       </c>
       <c r="BQ146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR146" t="n">
         <v>0</v>
       </c>
       <c r="BS146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU146" t="n">
         <v>1</v>
       </c>
       <c r="BV146" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="BW146" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BX146" t="n">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="BY146" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="BZ146" t="n">
-        <v>2.48</v>
+        <v>1.83</v>
       </c>
       <c r="CA146" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="CB146" t="n">
-        <v>4.45</v>
+        <v>3.61</v>
       </c>
       <c r="CC146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD146" t="n">
         <v>0</v>
       </c>
       <c r="CE146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF146" t="n">
         <v>0</v>
@@ -70723,7 +70723,7 @@
         <v>0</v>
       </c>
       <c r="CM146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN146" t="n">
         <v>0</v>
@@ -70732,22 +70732,22 @@
         <v>0</v>
       </c>
       <c r="CP146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ146" t="n">
         <v>1</v>
       </c>
       <c r="CR146" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="CS146" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="CT146" t="n">
         <v>1</v>
       </c>
       <c r="CU146" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CV146" t="n">
         <v>9</v>
@@ -70756,55 +70756,55 @@
         <v>1</v>
       </c>
       <c r="CX146" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CY146" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CZ146" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="DA146" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="DB146" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="DC146" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="DE146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF146" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="DG146" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="DH146" t="n">
         <v>1.23</v>
       </c>
       <c r="DI146" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="DJ146" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="DK146" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="DL146" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="DM146" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="DN146" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="DO146" t="n">
         <v>17</v>
@@ -70813,117 +70813,117 @@
         <v>1</v>
       </c>
       <c r="DQ146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW146" t="n">
-        <v>19.95</v>
+        <v>13.45</v>
       </c>
       <c r="DX146" t="n">
-        <v>8.640000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="DY146" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ146" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA146" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EB146" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EC146" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="ED146" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EE146" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EF146" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EG146" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EH146" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EI146" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EJ146" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EK146" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EL146" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EM146" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EN146" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EO146" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EP146" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -74105,7 +74105,7 @@
         <v>1</v>
       </c>
       <c r="DE153" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF153" t="n">
         <v>0.33</v>
@@ -74570,7 +74570,7 @@
         <v>50</v>
       </c>
       <c r="DD154" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE154" t="n">
         <v>0.5</v>
@@ -75707,146 +75707,146 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F157" s="2" t="n">
         <v>45983.72916666666</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I157" t="n">
         <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" t="n">
+        <v>8</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2</v>
+      </c>
+      <c r="S157" t="n">
+        <v>15</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1</v>
+      </c>
+      <c r="U157" t="n">
+        <v>23</v>
+      </c>
+      <c r="V157" t="n">
+        <v>3</v>
+      </c>
+      <c r="W157" t="n">
+        <v>18</v>
+      </c>
+      <c r="X157" t="n">
         <v>10</v>
       </c>
-      <c r="R157" t="n">
-        <v>4</v>
-      </c>
-      <c r="S157" t="n">
-        <v>12</v>
-      </c>
-      <c r="T157" t="n">
-        <v>3</v>
-      </c>
-      <c r="U157" t="n">
-        <v>22</v>
-      </c>
-      <c r="V157" t="n">
-        <v>7</v>
-      </c>
-      <c r="W157" t="n">
-        <v>8</v>
-      </c>
-      <c r="X157" t="n">
-        <v>17</v>
-      </c>
       <c r="Y157" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="Z157" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque</t>
+          <t>Estadio Municipal de Ipurúa</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>Calle Arquitectura, Leganés</t>
+          <t>Calle de Ipurúa, Eibar</t>
         </is>
       </c>
       <c r="AC157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD157" t="n">
         <v>4</v>
       </c>
       <c r="AE157" t="n">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF157" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI157" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AJ157" t="n">
-        <v>3.5</v>
+        <v>4.93</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL157" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AM157" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AO157" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AR157" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AS157" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AT157" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AU157" t="n">
         <v>3</v>
       </c>
       <c r="AV157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW157" t="n">
         <v>1</v>
@@ -75855,22 +75855,22 @@
         <v>0</v>
       </c>
       <c r="AY157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB157" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="BC157" t="n">
         <v>0</v>
       </c>
       <c r="BD157" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="BE157" t="n">
         <v>0</v>
@@ -75885,178 +75885,178 @@
         <v>1</v>
       </c>
       <c r="BI157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ157" t="n">
         <v>0</v>
       </c>
       <c r="BK157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM157" t="n">
         <v>4</v>
       </c>
-      <c r="BL157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM157" t="n">
-        <v>1</v>
-      </c>
       <c r="BN157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO157" t="n">
         <v>4</v>
       </c>
-      <c r="BO157" t="n">
-        <v>0</v>
-      </c>
       <c r="BP157" t="n">
         <v>2</v>
       </c>
       <c r="BQ157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR157" t="n">
         <v>2</v>
       </c>
       <c r="BS157" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BT157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU157" t="n">
         <v>1</v>
       </c>
       <c r="BV157" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW157" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX157" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY157" t="n">
+        <v>62</v>
+      </c>
+      <c r="BZ157" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CA157" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CB157" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR157" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS157" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU157" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV157" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY157" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ157" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA157" t="n">
         <v>57</v>
       </c>
-      <c r="BW157" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX157" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY157" t="n">
-        <v>47</v>
-      </c>
-      <c r="BZ157" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CA157" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CB157" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="CC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP157" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR157" t="n">
-        <v>23</v>
-      </c>
-      <c r="CS157" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU157" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV157" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW157" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX157" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY157" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ157" t="n">
-        <v>33</v>
-      </c>
-      <c r="DA157" t="n">
-        <v>67</v>
-      </c>
       <c r="DB157" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="DC157" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="DD157" t="n">
-        <v>0.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE157" t="n">
-        <v>1.67</v>
+        <v>0.89</v>
       </c>
       <c r="DF157" t="n">
-        <v>0.83</v>
+        <v>2.14</v>
       </c>
       <c r="DG157" t="n">
-        <v>1.5</v>
+        <v>0.57</v>
       </c>
       <c r="DH157" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="DI157" t="n">
-        <v>1.92</v>
+        <v>0.64</v>
       </c>
       <c r="DJ157" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="DK157" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="DL157" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="DM157" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="DN157" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="DO157" t="n">
         <v>17</v>
@@ -76080,81 +76080,97 @@
         <v>0</v>
       </c>
       <c r="DV157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW157" t="n">
-        <v>7.24</v>
+        <v>6.63</v>
       </c>
       <c r="DX157" t="n">
-        <v>3.97</v>
+        <v>2.71</v>
       </c>
       <c r="DY157" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="DZ157" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA157" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EB157" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EC157" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="ED157" t="inlineStr">
         <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EE157" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EF157" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EG157" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EH157" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI157" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EJ157" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EK157" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="EL157" t="inlineStr">
+        <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="EE157" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EF157" t="inlineStr"/>
-      <c r="EG157" t="inlineStr"/>
-      <c r="EH157" t="inlineStr"/>
-      <c r="EI157" t="inlineStr"/>
-      <c r="EJ157" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="EK157" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="EL157" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
       <c r="EM157" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EN157" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EO157" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EP157" t="inlineStr">
@@ -76179,146 +76195,146 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F158" s="2" t="n">
         <v>45983.72916666666</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
         <v>3</v>
       </c>
       <c r="J158" t="n">
+        <v>5</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>5</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>10</v>
+      </c>
+      <c r="R158" t="n">
+        <v>4</v>
+      </c>
+      <c r="S158" t="n">
+        <v>12</v>
+      </c>
+      <c r="T158" t="n">
+        <v>3</v>
+      </c>
+      <c r="U158" t="n">
+        <v>22</v>
+      </c>
+      <c r="V158" t="n">
         <v>7</v>
       </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>7</v>
-      </c>
-      <c r="M158" t="n">
-        <v>6</v>
-      </c>
-      <c r="N158" t="n">
-        <v>3</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q158" t="n">
+      <c r="W158" t="n">
         <v>8</v>
       </c>
-      <c r="R158" t="n">
-        <v>2</v>
-      </c>
-      <c r="S158" t="n">
-        <v>15</v>
-      </c>
-      <c r="T158" t="n">
-        <v>1</v>
-      </c>
-      <c r="U158" t="n">
-        <v>23</v>
-      </c>
-      <c r="V158" t="n">
-        <v>3</v>
-      </c>
-      <c r="W158" t="n">
-        <v>18</v>
-      </c>
       <c r="X158" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Y158" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Z158" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Ipurúa</t>
+          <t>Estadio Municipal de Butarque</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>Calle de Ipurúa, Eibar</t>
+          <t>Calle Arquitectura, Leganés</t>
         </is>
       </c>
       <c r="AC158" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD158" t="n">
         <v>4</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AF158" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AG158" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI158" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="AJ158" t="n">
-        <v>4.93</v>
+        <v>3.5</v>
       </c>
       <c r="AK158" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AL158" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AN158" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AO158" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AR158" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AS158" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AT158" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AU158" t="n">
         <v>3</v>
       </c>
       <c r="AV158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW158" t="n">
         <v>1</v>
@@ -76327,22 +76343,22 @@
         <v>0</v>
       </c>
       <c r="AY158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB158" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="BC158" t="n">
         <v>0</v>
       </c>
       <c r="BD158" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="BE158" t="n">
         <v>0</v>
@@ -76357,178 +76373,178 @@
         <v>1</v>
       </c>
       <c r="BI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK158" t="n">
         <v>4</v>
       </c>
-      <c r="BJ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK158" t="n">
-        <v>3</v>
-      </c>
       <c r="BL158" t="n">
         <v>0</v>
       </c>
       <c r="BM158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN158" t="n">
         <v>4</v>
       </c>
-      <c r="BN158" t="n">
-        <v>3</v>
-      </c>
       <c r="BO158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP158" t="n">
         <v>2</v>
       </c>
       <c r="BQ158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR158" t="n">
         <v>2</v>
       </c>
       <c r="BS158" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BT158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU158" t="n">
         <v>1</v>
       </c>
       <c r="BV158" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="BW158" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX158" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY158" t="n">
+        <v>47</v>
+      </c>
+      <c r="BZ158" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CA158" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB158" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR158" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS158" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU158" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV158" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX158" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY158" t="n">
         <v>12</v>
       </c>
-      <c r="BX158" t="n">
+      <c r="CZ158" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA158" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB158" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC158" t="n">
         <v>83</v>
       </c>
-      <c r="BY158" t="n">
-        <v>62</v>
-      </c>
-      <c r="BZ158" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CA158" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="CB158" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR158" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS158" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU158" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV158" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW158" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX158" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY158" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ158" t="n">
-        <v>36</v>
-      </c>
-      <c r="DA158" t="n">
-        <v>57</v>
-      </c>
-      <c r="DB158" t="n">
-        <v>7</v>
-      </c>
-      <c r="DC158" t="n">
-        <v>57</v>
-      </c>
       <c r="DD158" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE158" t="n">
         <v>1.67</v>
       </c>
-      <c r="DE158" t="n">
-        <v>0.89</v>
-      </c>
       <c r="DF158" t="n">
-        <v>2.14</v>
+        <v>0.83</v>
       </c>
       <c r="DG158" t="n">
-        <v>0.57</v>
+        <v>1.5</v>
       </c>
       <c r="DH158" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="DI158" t="n">
-        <v>0.64</v>
+        <v>1.92</v>
       </c>
       <c r="DJ158" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="DK158" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="DL158" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="DM158" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DN158" t="n">
-        <v>3.22</v>
+        <v>2.71</v>
       </c>
       <c r="DO158" t="n">
         <v>17</v>
@@ -76552,97 +76568,81 @@
         <v>0</v>
       </c>
       <c r="DV158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW158" t="n">
-        <v>6.63</v>
+        <v>7.24</v>
       </c>
       <c r="DX158" t="n">
-        <v>2.71</v>
+        <v>3.97</v>
       </c>
       <c r="DY158" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ158" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="EA158" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EB158" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EC158" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="ED158" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EE158" t="inlineStr">
         <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EF158" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EG158" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EH158" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EI158" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EF158" t="inlineStr"/>
+      <c r="EG158" t="inlineStr"/>
+      <c r="EH158" t="inlineStr"/>
+      <c r="EI158" t="inlineStr"/>
       <c r="EJ158" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EK158" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EL158" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EM158" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EN158" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EO158" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EP158" t="inlineStr">
@@ -81778,7 +81778,7 @@
         <v>64</v>
       </c>
       <c r="DD169" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE169" t="n">
         <v>1.25</v>
@@ -82749,7 +82749,7 @@
         <v>2.13</v>
       </c>
       <c r="DE171" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF171" t="n">
         <v>2.29</v>
@@ -87782,13 +87782,13 @@
         <v>4</v>
       </c>
       <c r="T182" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U182" t="n">
         <v>6</v>
       </c>
       <c r="V182" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W182" t="n">
         <v>17</v>
@@ -87963,10 +87963,10 @@
         <v>0.89</v>
       </c>
       <c r="CA182" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="CB182" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="CC182" t="n">
         <v>0</v>
@@ -88219,12 +88219,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F183" s="2" t="n">
@@ -88234,155 +88234,155 @@
         <v>1</v>
       </c>
       <c r="H183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J183" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K183" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L183" t="n">
         <v>12</v>
       </c>
       <c r="M183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N183" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
       </c>
       <c r="Q183" t="n">
+        <v>3</v>
+      </c>
+      <c r="R183" t="n">
         <v>5</v>
       </c>
-      <c r="R183" t="n">
-        <v>3</v>
-      </c>
       <c r="S183" t="n">
+        <v>3</v>
+      </c>
+      <c r="T183" t="n">
+        <v>12</v>
+      </c>
+      <c r="U183" t="n">
+        <v>6</v>
+      </c>
+      <c r="V183" t="n">
         <v>17</v>
       </c>
-      <c r="T183" t="n">
-        <v>9</v>
-      </c>
-      <c r="U183" t="n">
-        <v>22</v>
-      </c>
-      <c r="V183" t="n">
-        <v>12</v>
-      </c>
       <c r="W183" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X183" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Y183" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="Z183" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Ipurúa</t>
+          <t>Estadio Abanca-Riazor</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>Calle de Ipurúa, Eibar</t>
+          <t>Calle Manuel Murguía, La Coruña</t>
         </is>
       </c>
       <c r="AC183" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD183" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="AF183" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AG183" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="AH183" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AI183" t="n">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="AJ183" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="AK183" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AL183" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AM183" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AN183" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AO183" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.38</v>
       </c>
       <c r="AR183" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AS183" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="AT183" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AU183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV183" t="n">
         <v>1</v>
       </c>
       <c r="AW183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX183" t="n">
         <v>0</v>
       </c>
       <c r="AY183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB183" t="n">
-        <v>1023</v>
+        <v>6257</v>
       </c>
       <c r="BC183" t="n">
         <v>0</v>
       </c>
       <c r="BD183" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="BE183" t="n">
         <v>0</v>
@@ -88400,73 +88400,73 @@
         <v>2</v>
       </c>
       <c r="BJ183" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM183" t="n">
         <v>6</v>
       </c>
-      <c r="BL183" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM183" t="n">
+      <c r="BN183" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR183" t="n">
         <v>4</v>
       </c>
-      <c r="BN183" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ183" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR183" t="n">
-        <v>2</v>
-      </c>
       <c r="BS183" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BT183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU183" t="n">
         <v>1</v>
       </c>
       <c r="BV183" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="BW183" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="BX183" t="n">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="BY183" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="BZ183" t="n">
-        <v>2.28</v>
+        <v>0.78</v>
       </c>
       <c r="CA183" t="n">
-        <v>1.13</v>
+        <v>1.83</v>
       </c>
       <c r="CB183" t="n">
-        <v>3.41</v>
+        <v>2.6</v>
       </c>
       <c r="CC183" t="n">
         <v>0</v>
       </c>
       <c r="CD183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE183" t="n">
         <v>0</v>
       </c>
       <c r="CF183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG183" t="n">
         <v>0</v>
@@ -88487,7 +88487,7 @@
         <v>0</v>
       </c>
       <c r="CM183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN183" t="n">
         <v>0</v>
@@ -88502,73 +88502,73 @@
         <v>1</v>
       </c>
       <c r="CR183" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CS183" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU183" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV183" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX183" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY183" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ183" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA183" t="n">
+        <v>61</v>
+      </c>
+      <c r="DB183" t="n">
         <v>27</v>
       </c>
-      <c r="CT183" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU183" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV183" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW183" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX183" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY183" t="n">
-        <v>15</v>
-      </c>
-      <c r="CZ183" t="n">
-        <v>57</v>
-      </c>
-      <c r="DA183" t="n">
-        <v>69</v>
-      </c>
-      <c r="DB183" t="n">
-        <v>38</v>
-      </c>
       <c r="DC183" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="DD183" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="DE183" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="DF183" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="DG183" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DH183" t="n">
-        <v>1.06</v>
+        <v>2</v>
       </c>
       <c r="DI183" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="DJ183" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="DK183" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="DL183" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="DM183" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="DN183" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="DO183" t="n">
         <v>17</v>
@@ -88583,7 +88583,7 @@
         <v>1</v>
       </c>
       <c r="DS183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT183" t="b">
         <v>0</v>
@@ -88595,14 +88595,14 @@
         <v>1</v>
       </c>
       <c r="DW183" t="n">
-        <v>14.93</v>
+        <v>15.88</v>
       </c>
       <c r="DX183" t="n">
-        <v>4.24</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DY183" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="DZ183" t="inlineStr">
@@ -88612,82 +88612,66 @@
       </c>
       <c r="EA183" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EB183" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EC183" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="ED183" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EE183" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EF183" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EG183" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EH183" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EI183" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF183" t="inlineStr"/>
+      <c r="EG183" t="inlineStr"/>
+      <c r="EH183" t="inlineStr"/>
+      <c r="EI183" t="inlineStr"/>
       <c r="EJ183" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="EK183" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EL183" t="inlineStr">
         <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EM183" t="inlineStr">
+        <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="EM183" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="EN183" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EO183" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EP183" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.33</t>
         </is>
       </c>
     </row>
@@ -88707,12 +88691,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F184" s="2" t="n">
@@ -88722,155 +88706,155 @@
         <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I184" t="n">
+        <v>3</v>
+      </c>
+      <c r="J184" t="n">
+        <v>8</v>
+      </c>
+      <c r="K184" t="n">
         <v>4</v>
-      </c>
-      <c r="J184" t="n">
-        <v>3</v>
-      </c>
-      <c r="K184" t="n">
-        <v>9</v>
       </c>
       <c r="L184" t="n">
         <v>12</v>
       </c>
       <c r="M184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N184" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R184" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S184" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T184" t="n">
+        <v>9</v>
+      </c>
+      <c r="U184" t="n">
+        <v>23</v>
+      </c>
+      <c r="V184" t="n">
         <v>12</v>
       </c>
-      <c r="U184" t="n">
-        <v>6</v>
-      </c>
-      <c r="V184" t="n">
-        <v>17</v>
-      </c>
       <c r="W184" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X184" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y184" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="Z184" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>Estadio Abanca-Riazor</t>
+          <t>Estadio Municipal de Ipurúa</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>Calle Manuel Murguía, La Coruña</t>
+          <t>Calle de Ipurúa, Eibar</t>
         </is>
       </c>
       <c r="AC184" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD184" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE184" t="n">
-        <v>2.42</v>
+        <v>1.74</v>
       </c>
       <c r="AF184" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AG184" t="n">
-        <v>2.85</v>
+        <v>4.8</v>
       </c>
       <c r="AH184" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AI184" t="n">
-        <v>1.86</v>
+        <v>2.21</v>
       </c>
       <c r="AJ184" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="AK184" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AL184" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AM184" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AN184" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AO184" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.38</v>
       </c>
       <c r="AR184" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AS184" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="AT184" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AU184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV184" t="n">
         <v>1</v>
       </c>
       <c r="AW184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX184" t="n">
         <v>0</v>
       </c>
       <c r="AY184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB184" t="n">
-        <v>6257</v>
+        <v>1023</v>
       </c>
       <c r="BC184" t="n">
         <v>0</v>
       </c>
       <c r="BD184" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="BE184" t="n">
         <v>0</v>
@@ -88888,73 +88872,73 @@
         <v>2</v>
       </c>
       <c r="BJ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM184" t="n">
         <v>4</v>
       </c>
-      <c r="BK184" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL184" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM184" t="n">
-        <v>6</v>
-      </c>
       <c r="BN184" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BO184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BP184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS184" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT184" t="n">
         <v>4</v>
       </c>
-      <c r="BS184" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT184" t="n">
-        <v>5</v>
-      </c>
       <c r="BU184" t="n">
         <v>1</v>
       </c>
       <c r="BV184" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="BW184" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="BX184" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="BY184" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="BZ184" t="n">
-        <v>0.78</v>
+        <v>2.34</v>
       </c>
       <c r="CA184" t="n">
-        <v>1.83</v>
+        <v>1.13</v>
       </c>
       <c r="CB184" t="n">
-        <v>2.6</v>
+        <v>3.47</v>
       </c>
       <c r="CC184" t="n">
         <v>0</v>
       </c>
       <c r="CD184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE184" t="n">
         <v>0</v>
       </c>
       <c r="CF184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG184" t="n">
         <v>0</v>
@@ -88975,7 +88959,7 @@
         <v>0</v>
       </c>
       <c r="CM184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN184" t="n">
         <v>0</v>
@@ -88990,73 +88974,73 @@
         <v>1</v>
       </c>
       <c r="CR184" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="CS184" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="CT184" t="n">
         <v>1</v>
       </c>
       <c r="CU184" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV184" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW184" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX184" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY184" t="n">
         <v>15</v>
       </c>
-      <c r="CV184" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW184" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX184" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY184" t="n">
-        <v>3</v>
-      </c>
       <c r="CZ184" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="DA184" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="DB184" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="DC184" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="DD184" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE184" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF184" t="n">
         <v>1.88</v>
       </c>
-      <c r="DE184" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="DF184" t="n">
-        <v>2.14</v>
-      </c>
       <c r="DG184" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DH184" t="n">
-        <v>2</v>
+        <v>1.06</v>
       </c>
       <c r="DI184" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="DJ184" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="DK184" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="DL184" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="DM184" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="DN184" t="n">
-        <v>2.93</v>
+        <v>3.24</v>
       </c>
       <c r="DO184" t="n">
         <v>17</v>
@@ -89071,7 +89055,7 @@
         <v>1</v>
       </c>
       <c r="DS184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT184" t="b">
         <v>0</v>
@@ -89083,14 +89067,14 @@
         <v>1</v>
       </c>
       <c r="DW184" t="n">
-        <v>15.88</v>
+        <v>14.93</v>
       </c>
       <c r="DX184" t="n">
-        <v>9.630000000000001</v>
+        <v>4.24</v>
       </c>
       <c r="DY184" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="DZ184" t="inlineStr">
@@ -89100,66 +89084,82 @@
       </c>
       <c r="EA184" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EB184" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EC184" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="ED184" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EE184" t="inlineStr">
         <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EF184" t="inlineStr"/>
-      <c r="EG184" t="inlineStr"/>
-      <c r="EH184" t="inlineStr"/>
-      <c r="EI184" t="inlineStr"/>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EF184" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EG184" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EH184" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EI184" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
       <c r="EJ184" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EK184" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="EL184" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EM184" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EN184" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EO184" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EP184" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
@@ -91098,6 +91098,478 @@
       </c>
       <c r="EO188" t="inlineStr"/>
       <c r="EP188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Spain_Segunda_División_2025-2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>18</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Cultural y Deportiva Leonesa</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>SD Huesca</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>46003.8125</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2</v>
+      </c>
+      <c r="I189" t="n">
+        <v>2</v>
+      </c>
+      <c r="J189" t="n">
+        <v>5</v>
+      </c>
+      <c r="K189" t="n">
+        <v>7</v>
+      </c>
+      <c r="L189" t="n">
+        <v>12</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>7</v>
+      </c>
+      <c r="R189" t="n">
+        <v>4</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="n">
+        <v>4</v>
+      </c>
+      <c r="U189" t="n">
+        <v>17</v>
+      </c>
+      <c r="V189" t="n">
+        <v>8</v>
+      </c>
+      <c r="W189" t="n">
+        <v>7</v>
+      </c>
+      <c r="X189" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Reino de León</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>Paseo Sáenz de Miera, León</t>
+        </is>
+      </c>
+      <c r="AC189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>301</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV189" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW189" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX189" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY189" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ189" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CA189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB189" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CC189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN189" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP189" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR189" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS189" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU189" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV189" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW189" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX189" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY189" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ189" t="n">
+        <v>32</v>
+      </c>
+      <c r="DA189" t="n">
+        <v>38</v>
+      </c>
+      <c r="DB189" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC189" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD189" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE189" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF189" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG189" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH189" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI189" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DJ189" t="n">
+        <v>69</v>
+      </c>
+      <c r="DK189" t="n">
+        <v>63</v>
+      </c>
+      <c r="DL189" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DM189" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN189" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DO189" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP189" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ189" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR189" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS189" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT189" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU189" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV189" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW189" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="DX189" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="DY189" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="DZ189" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA189" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EB189" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EC189" t="inlineStr">
+        <is>
+          <t>5.28</t>
+        </is>
+      </c>
+      <c r="ED189" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EE189" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EF189" t="inlineStr"/>
+      <c r="EG189" t="inlineStr"/>
+      <c r="EH189" t="inlineStr"/>
+      <c r="EI189" t="inlineStr"/>
+      <c r="EJ189" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EK189" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="EL189" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EM189" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EN189" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EO189" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EP189" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
